--- a/FreeLayout/Textfile/Export_Scraplist.xlsx
+++ b/FreeLayout/Textfile/Export_Scraplist.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>MONTHLY SCRAP LIST</t>
   </si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Section : </t>
   </si>
   <si>
-    <t>MCS</t>
+    <t>PUS</t>
   </si>
   <si>
     <t>No.</t>
@@ -271,55 +271,46 @@
     <t/>
   </si>
   <si>
-    <t>K1KA20AA0184</t>
-  </si>
-  <si>
-    <t>ECN_Immediate change 20240403-051</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>B0JDSL000013</t>
+  </si>
+  <si>
+    <t>ECN small Amout-No Plan</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
   <si>
     <t>5210</t>
   </si>
   <si>
-    <t>DESKTOCK_TEST</t>
-  </si>
-  <si>
-    <t>B0JDSL000013</t>
-  </si>
-  <si>
-    <t>ECN small Amout-No Plan</t>
+    <t>DESKtock_2</t>
+  </si>
+  <si>
+    <t>B0JCSL000018</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>B0JCSL000018</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>F1H1H221B052</t>
   </si>
   <si>
+    <t>ECN small Amout-No Plan &amp; other model discont</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>D0GB105JA084</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>D0GA303ZA038</t>
+  </si>
+  <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>D0GB105JA084</t>
-  </si>
-  <si>
-    <t>ECN small Amout-No Plan &amp; other model discont</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>D0GA303ZA038</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -1829,19 +1820,19 @@
         <v>71</v>
       </c>
       <c r="G12" s="42">
-        <v>8998</v>
+        <v>242</v>
       </c>
       <c r="H12" s="43">
-        <v>0.16559</v>
+        <v>0.09679</v>
       </c>
       <c r="I12" s="44">
-        <v>1489.97998</v>
+        <v>23.43</v>
       </c>
       <c r="J12" s="43">
-        <v>0.1577</v>
+        <v>0.09679</v>
       </c>
       <c r="K12" s="44">
-        <v>1419.05004</v>
+        <v>23.43</v>
       </c>
       <c r="L12" s="45" t="s">
         <v>72</v>
@@ -1905,25 +1896,25 @@
         <v>76</v>
       </c>
       <c r="G13" s="42">
-        <v>242</v>
+        <v>142</v>
       </c>
       <c r="H13" s="43">
-        <v>0.09679</v>
+        <v>0.13093</v>
       </c>
       <c r="I13" s="44">
-        <v>23.43</v>
+        <v>18.59</v>
       </c>
       <c r="J13" s="43">
-        <v>0.09679</v>
+        <v>0.13093</v>
       </c>
       <c r="K13" s="44">
-        <v>23.43</v>
+        <v>18.59</v>
       </c>
       <c r="L13" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M13" s="45" t="s">
         <v>77</v>
-      </c>
-      <c r="M13" s="45" t="s">
-        <v>78</v>
       </c>
       <c r="N13" s="46" t="s">
         <v>74</v>
@@ -1978,25 +1969,25 @@
         <v>70</v>
       </c>
       <c r="F14" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="42">
+        <v>119</v>
+      </c>
+      <c r="H14" s="43">
+        <v>0.00179</v>
+      </c>
+      <c r="I14" s="44">
+        <v>0.20999</v>
+      </c>
+      <c r="J14" s="43">
+        <v>0.00179</v>
+      </c>
+      <c r="K14" s="44">
+        <v>0.20999</v>
+      </c>
+      <c r="L14" s="45" t="s">
         <v>79</v>
-      </c>
-      <c r="G14" s="42">
-        <v>142</v>
-      </c>
-      <c r="H14" s="43">
-        <v>0.13093</v>
-      </c>
-      <c r="I14" s="44">
-        <v>18.59</v>
-      </c>
-      <c r="J14" s="43">
-        <v>0.13093</v>
-      </c>
-      <c r="K14" s="44">
-        <v>18.59</v>
-      </c>
-      <c r="L14" s="45" t="s">
-        <v>77</v>
       </c>
       <c r="M14" s="45" t="s">
         <v>80</v>
@@ -2057,22 +2048,22 @@
         <v>81</v>
       </c>
       <c r="G15" s="54">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="H15" s="43">
-        <v>0.00179</v>
+        <v>0.00041</v>
       </c>
       <c r="I15" s="44">
-        <v>0.20999</v>
+        <v>0.03999</v>
       </c>
       <c r="J15" s="43">
-        <v>0.00179</v>
+        <v>0.00041</v>
       </c>
       <c r="K15" s="44">
-        <v>0.20999</v>
+        <v>0.03999</v>
       </c>
       <c r="L15" s="45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M15" s="45" t="s">
         <v>82</v>
@@ -2133,25 +2124,25 @@
         <v>83</v>
       </c>
       <c r="G16" s="54">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="H16" s="43">
-        <v>0.00041</v>
+        <v>0.00069</v>
       </c>
       <c r="I16" s="44">
         <v>0.03999</v>
       </c>
       <c r="J16" s="43">
-        <v>0.00041</v>
+        <v>0.00069</v>
       </c>
       <c r="K16" s="44">
         <v>0.03999</v>
       </c>
       <c r="L16" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="M16" s="45" t="s">
         <v>84</v>
-      </c>
-      <c r="M16" s="45" t="s">
-        <v>85</v>
       </c>
       <c r="N16" s="46" t="s">
         <v>74</v>
@@ -2190,69 +2181,27 @@
       <c r="AF16" s="46"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="8" customFormat="1">
-      <c r="A17" s="38">
-        <v>6</v>
-      </c>
-      <c r="B17" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="54">
-        <v>60</v>
-      </c>
-      <c r="H17" s="43">
-        <v>0.00069</v>
-      </c>
-      <c r="I17" s="44">
-        <v>0.03999</v>
-      </c>
-      <c r="J17" s="43">
-        <v>0.00069</v>
-      </c>
-      <c r="K17" s="44">
-        <v>0.03999</v>
-      </c>
-      <c r="L17" s="45" t="s">
-        <v>84</v>
-      </c>
-      <c r="M17" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="N17" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="O17" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q17" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="R17" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="S17" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="T17" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="U17" s="50" t="s">
-        <v>70</v>
-      </c>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="45"/>
+      <c r="M17" s="45"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="55"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="47"/>
+      <c r="U17" s="50"/>
       <c r="V17" s="46"/>
       <c r="W17" s="51"/>
       <c r="X17" s="46"/>

--- a/FreeLayout/Textfile/Export_Scraplist.xlsx
+++ b/FreeLayout/Textfile/Export_Scraplist.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t>MONTHLY SCRAP LIST</t>
   </si>
@@ -63,13 +63,13 @@
     <t>Month :</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t xml:space="preserve">Section : </t>
   </si>
   <si>
-    <t>PUS</t>
+    <t>MCS</t>
   </si>
   <si>
     <t>No.</t>
@@ -271,46 +271,55 @@
     <t/>
   </si>
   <si>
+    <t>K1KA20AA0184</t>
+  </si>
+  <si>
+    <t>ECN_Immediate change 20240403-051</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5210</t>
+  </si>
+  <si>
+    <t>destock</t>
+  </si>
+  <si>
     <t>B0JDSL000013</t>
   </si>
   <si>
     <t>ECN small Amout-No Plan</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>B0JCSL000018</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>5210</t>
-  </si>
-  <si>
-    <t>DESKtock_2</t>
-  </si>
-  <si>
-    <t>B0JCSL000018</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>F1H1H221B052</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>D0GB105JA084</t>
+  </si>
+  <si>
     <t>ECN small Amout-No Plan &amp; other model discont</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>D0GA303ZA038</t>
+  </si>
+  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>D0GB105JA084</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>D0GA303ZA038</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>
@@ -1820,19 +1829,19 @@
         <v>71</v>
       </c>
       <c r="G12" s="42">
-        <v>242</v>
+        <v>8998</v>
       </c>
       <c r="H12" s="43">
-        <v>0.09679</v>
+        <v>0.16559</v>
       </c>
       <c r="I12" s="44">
-        <v>23.43</v>
+        <v>1489.97998</v>
       </c>
       <c r="J12" s="43">
-        <v>0.09679</v>
+        <v>0.1577</v>
       </c>
       <c r="K12" s="44">
-        <v>23.43</v>
+        <v>1419.05004</v>
       </c>
       <c r="L12" s="45" t="s">
         <v>72</v>
@@ -1862,7 +1871,7 @@
         <v>70</v>
       </c>
       <c r="U12" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V12" s="46"/>
       <c r="W12" s="51"/>
@@ -1896,25 +1905,25 @@
         <v>76</v>
       </c>
       <c r="G13" s="42">
-        <v>142</v>
+        <v>242</v>
       </c>
       <c r="H13" s="43">
-        <v>0.13093</v>
+        <v>0.09679</v>
       </c>
       <c r="I13" s="44">
-        <v>18.59</v>
+        <v>23.43</v>
       </c>
       <c r="J13" s="43">
-        <v>0.13093</v>
+        <v>0.09679</v>
       </c>
       <c r="K13" s="44">
-        <v>18.59</v>
+        <v>23.43</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M13" s="45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N13" s="46" t="s">
         <v>74</v>
@@ -1938,7 +1947,7 @@
         <v>70</v>
       </c>
       <c r="U13" s="50" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="V13" s="46"/>
       <c r="W13" s="51"/>
@@ -1969,25 +1978,25 @@
         <v>70</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" s="42">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="H14" s="43">
-        <v>0.00179</v>
+        <v>0.13093</v>
       </c>
       <c r="I14" s="44">
-        <v>0.20999</v>
+        <v>18.59</v>
       </c>
       <c r="J14" s="43">
-        <v>0.00179</v>
+        <v>0.13093</v>
       </c>
       <c r="K14" s="44">
-        <v>0.20999</v>
+        <v>18.59</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M14" s="45" t="s">
         <v>80</v>
@@ -2014,7 +2023,7 @@
         <v>70</v>
       </c>
       <c r="U14" s="50" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="V14" s="46"/>
       <c r="W14" s="51"/>
@@ -2048,22 +2057,22 @@
         <v>81</v>
       </c>
       <c r="G15" s="54">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="H15" s="43">
-        <v>0.00041</v>
+        <v>0.00179</v>
       </c>
       <c r="I15" s="44">
-        <v>0.03999</v>
+        <v>0.20999</v>
       </c>
       <c r="J15" s="43">
-        <v>0.00041</v>
+        <v>0.00179</v>
       </c>
       <c r="K15" s="44">
-        <v>0.03999</v>
+        <v>0.20999</v>
       </c>
       <c r="L15" s="45" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M15" s="45" t="s">
         <v>82</v>
@@ -2090,7 +2099,7 @@
         <v>70</v>
       </c>
       <c r="U15" s="50" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="V15" s="46"/>
       <c r="W15" s="51"/>
@@ -2124,25 +2133,25 @@
         <v>83</v>
       </c>
       <c r="G16" s="54">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="H16" s="43">
-        <v>0.00069</v>
+        <v>0.00041</v>
       </c>
       <c r="I16" s="44">
         <v>0.03999</v>
       </c>
       <c r="J16" s="43">
-        <v>0.00069</v>
+        <v>0.00041</v>
       </c>
       <c r="K16" s="44">
         <v>0.03999</v>
       </c>
       <c r="L16" s="45" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N16" s="46" t="s">
         <v>74</v>
@@ -2166,7 +2175,7 @@
         <v>70</v>
       </c>
       <c r="U16" s="50" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="V16" s="46"/>
       <c r="W16" s="51"/>
@@ -2181,27 +2190,69 @@
       <c r="AF16" s="46"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="8" customFormat="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="54"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="46"/>
-      <c r="O17" s="55"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="53"/>
-      <c r="T17" s="47"/>
-      <c r="U17" s="50"/>
+      <c r="A17" s="38">
+        <v>6</v>
+      </c>
+      <c r="B17" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="54">
+        <v>60</v>
+      </c>
+      <c r="H17" s="43">
+        <v>0.00069</v>
+      </c>
+      <c r="I17" s="44">
+        <v>0.03999</v>
+      </c>
+      <c r="J17" s="43">
+        <v>0.00069</v>
+      </c>
+      <c r="K17" s="44">
+        <v>0.03999</v>
+      </c>
+      <c r="L17" s="45" t="s">
+        <v>84</v>
+      </c>
+      <c r="M17" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="N17" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q17" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="R17" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="T17" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="U17" s="50" t="s">
+        <v>86</v>
+      </c>
       <c r="V17" s="46"/>
       <c r="W17" s="51"/>
       <c r="X17" s="46"/>

--- a/FreeLayout/Textfile/Export_Scraplist.xlsx
+++ b/FreeLayout/Textfile/Export_Scraplist.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t>MONTHLY SCRAP LIST</t>
   </si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Section : </t>
   </si>
   <si>
-    <t>MCS</t>
+    <t>PUR</t>
   </si>
   <si>
     <t>No.</t>
@@ -265,61 +265,223 @@
     <t>(32)</t>
   </si>
   <si>
-    <t>VB01</t>
+    <t>VR01</t>
+  </si>
+  <si>
+    <t>1239</t>
+  </si>
+  <si>
+    <t>NA2000</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>K1KA20AA0184</t>
-  </si>
-  <si>
-    <t>ECN_Immediate change 20240403-051</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>5210</t>
-  </si>
-  <si>
-    <t>destock</t>
-  </si>
-  <si>
-    <t>B0JDSL000013</t>
-  </si>
-  <si>
-    <t>ECN small Amout-No Plan</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>B0JCSL000018</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>F1H1H221B052</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>D0GB105JA084</t>
-  </si>
-  <si>
-    <t>ECN small Amout-No Plan &amp; other model discont</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>D0GA303ZA038</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>PNKM1188ZA1/AS</t>
+  </si>
+  <si>
+    <t>VF013</t>
+  </si>
+  <si>
+    <t>Claim scrap deadstock</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Halb</t>
+  </si>
+  <si>
+    <t>PNKM1188ZA2/AS</t>
+  </si>
+  <si>
+    <t>PNKM1204ZA1/AS</t>
+  </si>
+  <si>
+    <t>L0AD02A00049</t>
+  </si>
+  <si>
+    <t>L0DAYA000010</t>
+  </si>
+  <si>
+    <t>L5DYBYY00080</t>
+  </si>
+  <si>
+    <t>LSF500X300B</t>
+  </si>
+  <si>
+    <t>N4DHYYY00022</t>
+  </si>
+  <si>
+    <t>PNBC1354ZA1K108/V1</t>
+  </si>
+  <si>
+    <t>PNBC1354ZA7W252/V1</t>
+  </si>
+  <si>
+    <t>PNGP1138ZB1C100/V2</t>
+  </si>
+  <si>
+    <t>PNGP1138ZB2C100/V2</t>
+  </si>
+  <si>
+    <t>PNGTB123YA/V1</t>
+  </si>
+  <si>
+    <t>PNGTB123ZA/V1</t>
+  </si>
+  <si>
+    <t>PNJC1018ZB/Z1</t>
+  </si>
+  <si>
+    <t>PNJK1114ZA/V1</t>
+  </si>
+  <si>
+    <t>PNKF1137ZA2H577/V3</t>
+  </si>
+  <si>
+    <t>PNKF1137ZA3W252/V3</t>
+  </si>
+  <si>
+    <t>PNKF1137ZA4R236/V3</t>
+  </si>
+  <si>
+    <t>PNKF1137ZA6B591/V3</t>
+  </si>
+  <si>
+    <t>PNKM1186ZA1K108/V3</t>
+  </si>
+  <si>
+    <t>PNKM1186ZA2W252/V3</t>
+  </si>
+  <si>
+    <t>PNPD2346ZA/V1</t>
+  </si>
+  <si>
+    <t>PNPK3714010PA/V1</t>
+  </si>
+  <si>
+    <t>PNPK3715007PA/V3</t>
+  </si>
+  <si>
+    <t>PNPK3716009NA/V3</t>
+  </si>
+  <si>
+    <t>PNPK4330001ZA/V1</t>
+  </si>
+  <si>
+    <t>PNPK4330001ZA/V2</t>
+  </si>
+  <si>
+    <t>PNPK4331001ZA/V1</t>
+  </si>
+  <si>
+    <t>PNPK4331001ZA/V2</t>
+  </si>
+  <si>
+    <t>PNPK4331002ZA/V1</t>
+  </si>
+  <si>
+    <t>PNPP1154ZA/V1</t>
+  </si>
+  <si>
+    <t>PNPP1155ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA1881ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA1902ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA3532ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA3533ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA3707ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA8570XA/V1</t>
+  </si>
+  <si>
+    <t>PNQA8790ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA8791ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQA8973ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQH1027ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQT2640TA/V1</t>
+  </si>
+  <si>
+    <t>PNQT2640ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQV1181ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQW6198ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQW6199ZA/V1</t>
+  </si>
+  <si>
+    <t>PNQW6299ZA/V1</t>
+  </si>
+  <si>
+    <t>PNYE1042ZB/V1</t>
+  </si>
+  <si>
+    <t>PNYE1050ZA/V2</t>
+  </si>
+  <si>
+    <t>PNYF1129XA3H577/V2</t>
+  </si>
+  <si>
+    <t>PNYF1129XA4W252/V2</t>
+  </si>
+  <si>
+    <t>PNYF1129XA5R236/V3</t>
+  </si>
+  <si>
+    <t>PNYF1129XA7B591/V2</t>
+  </si>
+  <si>
+    <t>PNYF1129XA8V163/V3</t>
+  </si>
+  <si>
+    <t>PSPP1089ZA</t>
+  </si>
+  <si>
+    <t>RIB0N60A200</t>
+  </si>
+  <si>
+    <t>XZB05X08A03-LP</t>
+  </si>
+  <si>
+    <t>ZK3B110CR77BK</t>
+  </si>
+  <si>
+    <t>ZL1W580L1000T003</t>
+  </si>
+  <si>
+    <t>ZQ1ARTPP135X75A</t>
+  </si>
+  <si>
+    <t>ZQ4BW0153</t>
+  </si>
+  <si>
+    <t>ZT5LPT60X200B</t>
+  </si>
+  <si>
+    <t>ZU2BW6050</t>
   </si>
 </sst>
 </file>
@@ -1820,58 +1982,58 @@
         <v>70</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G12" s="42">
-        <v>8998</v>
+        <v>155</v>
       </c>
       <c r="H12" s="43">
-        <v>0.16559</v>
+        <v>0.09968</v>
       </c>
       <c r="I12" s="44">
-        <v>1489.97998</v>
+        <v>15.4504</v>
       </c>
       <c r="J12" s="43">
-        <v>0.1577</v>
+        <v>0</v>
       </c>
       <c r="K12" s="44">
-        <v>1419.05004</v>
+        <v>0</v>
       </c>
       <c r="L12" s="45" t="s">
         <v>72</v>
       </c>
       <c r="M12" s="45" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N12" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="P12" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P12" s="48">
+        <v>11</v>
       </c>
       <c r="Q12" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R12" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S12" s="49" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T12" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U12" s="50" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="V12" s="46"/>
       <c r="W12" s="51"/>
@@ -1896,58 +2058,58 @@
         <v>70</v>
       </c>
       <c r="D13" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E13" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G13" s="42">
-        <v>242</v>
+        <v>8</v>
       </c>
       <c r="H13" s="43">
-        <v>0.09679</v>
+        <v>0.11938</v>
       </c>
       <c r="I13" s="44">
-        <v>23.43</v>
+        <v>0.95504</v>
       </c>
       <c r="J13" s="43">
-        <v>0.09679</v>
+        <v>0</v>
       </c>
       <c r="K13" s="44">
-        <v>23.43</v>
+        <v>0</v>
       </c>
       <c r="L13" s="45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M13" s="45" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="P13" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P13" s="48">
+        <v>11</v>
       </c>
       <c r="Q13" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R13" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S13" s="49" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T13" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U13" s="50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V13" s="46"/>
       <c r="W13" s="51"/>
@@ -1972,58 +2134,58 @@
         <v>70</v>
       </c>
       <c r="D14" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E14" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F14" s="41" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="42">
-        <v>142</v>
+        <v>11</v>
       </c>
       <c r="H14" s="43">
-        <v>0.13093</v>
+        <v>0.06307</v>
       </c>
       <c r="I14" s="44">
-        <v>18.59</v>
+        <v>0.69377</v>
       </c>
       <c r="J14" s="43">
-        <v>0.13093</v>
+        <v>0</v>
       </c>
       <c r="K14" s="44">
-        <v>18.59</v>
+        <v>0</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M14" s="45" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N14" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O14" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P14" s="48">
+        <v>11</v>
       </c>
       <c r="Q14" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R14" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S14" s="53" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T14" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U14" s="50" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="V14" s="46"/>
       <c r="W14" s="51"/>
@@ -2048,58 +2210,58 @@
         <v>70</v>
       </c>
       <c r="D15" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E15" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" s="54">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="H15" s="43">
-        <v>0.00179</v>
+        <v>0.22268</v>
       </c>
       <c r="I15" s="44">
-        <v>0.20999</v>
+        <v>0.66804</v>
       </c>
       <c r="J15" s="43">
-        <v>0.00179</v>
+        <v>0</v>
       </c>
       <c r="K15" s="44">
-        <v>0.20999</v>
+        <v>0</v>
       </c>
       <c r="L15" s="45" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="M15" s="45" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="N15" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O15" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P15" s="48">
+        <v>11</v>
       </c>
       <c r="Q15" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R15" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S15" s="53" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T15" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U15" s="50" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="V15" s="46"/>
       <c r="W15" s="51"/>
@@ -2124,58 +2286,58 @@
         <v>70</v>
       </c>
       <c r="D16" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G16" s="54">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="H16" s="43">
-        <v>0.00041</v>
+        <v>0.0673</v>
       </c>
       <c r="I16" s="44">
-        <v>0.03999</v>
+        <v>0.0673</v>
       </c>
       <c r="J16" s="43">
-        <v>0.00041</v>
+        <v>0</v>
       </c>
       <c r="K16" s="44">
-        <v>0.03999</v>
+        <v>0</v>
       </c>
       <c r="L16" s="45" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="N16" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O16" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="P16" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P16" s="48">
+        <v>11</v>
       </c>
       <c r="Q16" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R16" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S16" s="53" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T16" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U16" s="50" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="V16" s="46"/>
       <c r="W16" s="51"/>
@@ -2200,58 +2362,58 @@
         <v>70</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G17" s="54">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H17" s="43">
-        <v>0.00069</v>
+        <v>0.462</v>
       </c>
       <c r="I17" s="44">
-        <v>0.03999</v>
+        <v>17.094</v>
       </c>
       <c r="J17" s="43">
-        <v>0.00069</v>
+        <v>0</v>
       </c>
       <c r="K17" s="44">
-        <v>0.03999</v>
+        <v>0</v>
       </c>
       <c r="L17" s="45" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="N17" s="46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O17" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+      <c r="P17" s="48">
+        <v>11</v>
       </c>
       <c r="Q17" s="48" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="R17" s="47" t="s">
         <v>4</v>
       </c>
       <c r="S17" s="53" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T17" s="47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="U17" s="50" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="V17" s="46"/>
       <c r="W17" s="51"/>
@@ -2266,27 +2428,69 @@
       <c r="AF17" s="46"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="8" customFormat="1">
-      <c r="A18" s="38"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="45"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="48"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="53"/>
-      <c r="T18" s="47"/>
-      <c r="U18" s="50"/>
+      <c r="A18" s="38">
+        <v>7</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="42">
+        <v>27</v>
+      </c>
+      <c r="H18" s="43">
+        <v>5.23</v>
+      </c>
+      <c r="I18" s="44">
+        <v>141.21</v>
+      </c>
+      <c r="J18" s="43">
+        <v>0</v>
+      </c>
+      <c r="K18" s="44">
+        <v>0</v>
+      </c>
+      <c r="L18" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="M18" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="N18" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="O18" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="P18" s="48">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="R18" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="T18" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="U18" s="50" t="s">
+        <v>77</v>
+      </c>
       <c r="V18" s="46"/>
       <c r="W18" s="51"/>
       <c r="X18" s="46"/>
@@ -2300,27 +2504,69 @@
       <c r="AF18" s="46"/>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="8" customFormat="1">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="67"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="69"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="73"/>
-      <c r="Q19" s="73"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="74"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="75"/>
+      <c r="A19" s="63">
+        <v>8</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="67">
+        <v>1572</v>
+      </c>
+      <c r="H19" s="68">
+        <v>0.1652</v>
+      </c>
+      <c r="I19" s="69">
+        <v>259.6944</v>
+      </c>
+      <c r="J19" s="68">
+        <v>0</v>
+      </c>
+      <c r="K19" s="69">
+        <v>0</v>
+      </c>
+      <c r="L19" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="P19" s="73">
+        <v>11</v>
+      </c>
+      <c r="Q19" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="R19" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="S19" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="T19" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="U19" s="75" t="s">
+        <v>77</v>
+      </c>
       <c r="V19" s="71"/>
       <c r="W19" s="76"/>
       <c r="X19" s="71"/>
@@ -2334,27 +2580,69 @@
       <c r="AF19" s="71"/>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="8" customFormat="1">
-      <c r="A20" s="78"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="79"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="78"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="82"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
+      <c r="A20" s="78">
+        <v>9</v>
+      </c>
+      <c r="B20" s="78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="78">
+        <v>58168</v>
+      </c>
+      <c r="H20" s="78">
+        <v>0.0189</v>
+      </c>
+      <c r="I20" s="78">
+        <v>1099.3752</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0</v>
+      </c>
+      <c r="K20" s="78">
+        <v>0</v>
+      </c>
+      <c r="L20" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="M20" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="78" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20" s="80" t="s">
+        <v>72</v>
+      </c>
+      <c r="P20" s="31">
+        <v>11</v>
+      </c>
+      <c r="Q20" s="81" t="s">
+        <v>72</v>
+      </c>
+      <c r="R20" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="82" t="s">
+        <v>75</v>
+      </c>
+      <c r="T20" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="U20" s="21" t="s">
+        <v>77</v>
+      </c>
       <c r="V20" s="21"/>
       <c r="W20" s="83"/>
       <c r="X20" s="21"/>
@@ -2368,27 +2656,69 @@
       <c r="AF20" s="21"/>
     </row>
     <row r="21">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="84"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="85"/>
-      <c r="R21" s="85"/>
-      <c r="S21" s="85"/>
-      <c r="T21" s="85"/>
-      <c r="U21" s="85"/>
+      <c r="A21" s="15">
+        <v>10</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="16">
+        <v>106</v>
+      </c>
+      <c r="H21" s="17">
+        <v>0.02</v>
+      </c>
+      <c r="I21" s="17">
+        <v>2.12</v>
+      </c>
+      <c r="J21" s="17">
+        <v>0</v>
+      </c>
+      <c r="K21" s="17">
+        <v>0</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="M21" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R21" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T21" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U21" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V21" s="85"/>
       <c r="W21" s="85"/>
       <c r="X21" s="85"/>
@@ -2402,27 +2732,69 @@
       <c r="AF21" s="85"/>
     </row>
     <row r="22" s="4" customFormat="1">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
+      <c r="A22" s="5">
+        <v>11</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G22" s="20">
+        <v>58554</v>
+      </c>
+      <c r="H22" s="20">
+        <v>0.11847</v>
+      </c>
+      <c r="I22" s="20">
+        <v>6936.89238</v>
+      </c>
+      <c r="J22" s="20">
+        <v>0</v>
+      </c>
+      <c r="K22" s="20">
+        <v>0</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O22" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P22" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q22" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U22" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V22" s="20"/>
       <c r="W22" s="20"/>
       <c r="X22" s="20"/>
@@ -2436,27 +2808,69 @@
       <c r="AF22" s="20"/>
     </row>
     <row r="23" s="4" customFormat="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="86"/>
-      <c r="P23" s="20"/>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
+      <c r="A23" s="5">
+        <v>12</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" s="20">
+        <v>3350</v>
+      </c>
+      <c r="H23" s="20">
+        <v>0.13497</v>
+      </c>
+      <c r="I23" s="20">
+        <v>452.1495</v>
+      </c>
+      <c r="J23" s="20">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O23" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P23" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R23" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T23" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U23" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V23" s="20"/>
       <c r="W23" s="20"/>
       <c r="X23" s="20"/>
@@ -2470,27 +2884,69 @@
       <c r="AF23" s="20"/>
     </row>
     <row r="24" s="4" customFormat="1">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="86"/>
-      <c r="P24" s="20"/>
-      <c r="Q24" s="20"/>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
+      <c r="A24" s="5">
+        <v>13</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="20">
+        <v>1</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0.0148</v>
+      </c>
+      <c r="I24" s="20">
+        <v>0.0148</v>
+      </c>
+      <c r="J24" s="20">
+        <v>0</v>
+      </c>
+      <c r="K24" s="20">
+        <v>0</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O24" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P24" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R24" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T24" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U24" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V24" s="20"/>
       <c r="W24" s="20"/>
       <c r="X24" s="20"/>
@@ -2504,27 +2960,69 @@
       <c r="AF24" s="20"/>
     </row>
     <row r="25" s="4" customFormat="1">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="86"/>
-      <c r="P25" s="20"/>
-      <c r="Q25" s="20"/>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
+      <c r="A25" s="5">
+        <v>14</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G25" s="20">
+        <v>1</v>
+      </c>
+      <c r="H25" s="20">
+        <v>0.0091</v>
+      </c>
+      <c r="I25" s="20">
+        <v>0.0091</v>
+      </c>
+      <c r="J25" s="20">
+        <v>0</v>
+      </c>
+      <c r="K25" s="20">
+        <v>0</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N25" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O25" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P25" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q25" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S25" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T25" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U25" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V25" s="20"/>
       <c r="W25" s="20"/>
       <c r="X25" s="20"/>
@@ -2538,27 +3036,69 @@
       <c r="AF25" s="20"/>
     </row>
     <row r="26" s="4" customFormat="1">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="86"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
+      <c r="A26" s="5">
+        <v>15</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="20">
+        <v>2</v>
+      </c>
+      <c r="H26" s="20">
+        <v>0.021</v>
+      </c>
+      <c r="I26" s="20">
+        <v>0.042</v>
+      </c>
+      <c r="J26" s="20">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N26" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O26" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P26" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R26" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T26" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U26" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V26" s="20"/>
       <c r="W26" s="20"/>
       <c r="X26" s="20"/>
@@ -2572,27 +3112,69 @@
       <c r="AF26" s="20"/>
     </row>
     <row r="27" s="4" customFormat="1">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="86"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
+      <c r="A27" s="5">
+        <v>16</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G27" s="20">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20">
+        <v>0.218</v>
+      </c>
+      <c r="I27" s="20">
+        <v>0.218</v>
+      </c>
+      <c r="J27" s="20">
+        <v>0</v>
+      </c>
+      <c r="K27" s="20">
+        <v>0</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O27" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P27" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R27" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T27" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U27" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V27" s="20"/>
       <c r="W27" s="20"/>
       <c r="X27" s="20"/>
@@ -2606,27 +3188,69 @@
       <c r="AF27" s="20"/>
     </row>
     <row r="28" s="4" customFormat="1">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="86"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
+      <c r="A28" s="5">
+        <v>17</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="20">
+        <v>128</v>
+      </c>
+      <c r="H28" s="20">
+        <v>0.154</v>
+      </c>
+      <c r="I28" s="20">
+        <v>19.712</v>
+      </c>
+      <c r="J28" s="20">
+        <v>0</v>
+      </c>
+      <c r="K28" s="20">
+        <v>0</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N28" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O28" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P28" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q28" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R28" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S28" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T28" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U28" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V28" s="20"/>
       <c r="W28" s="20"/>
       <c r="X28" s="20"/>
@@ -2640,27 +3264,69 @@
       <c r="AF28" s="20"/>
     </row>
     <row r="29" s="4" customFormat="1">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="86"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="20"/>
-      <c r="R29" s="20"/>
-      <c r="S29" s="20"/>
-      <c r="T29" s="20"/>
-      <c r="U29" s="20"/>
+      <c r="A29" s="5">
+        <v>18</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="20">
+        <v>6</v>
+      </c>
+      <c r="H29" s="20">
+        <v>0.1654</v>
+      </c>
+      <c r="I29" s="20">
+        <v>0.9924</v>
+      </c>
+      <c r="J29" s="20">
+        <v>0</v>
+      </c>
+      <c r="K29" s="20">
+        <v>0</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N29" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O29" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P29" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R29" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T29" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U29" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V29" s="20"/>
       <c r="W29" s="20"/>
       <c r="X29" s="20"/>
@@ -2674,27 +3340,69 @@
       <c r="AF29" s="20"/>
     </row>
     <row r="30" s="4" customFormat="1">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="86"/>
-      <c r="P30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="T30" s="20"/>
-      <c r="U30" s="20"/>
+      <c r="A30" s="5">
+        <v>19</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="20">
+        <v>22</v>
+      </c>
+      <c r="H30" s="20">
+        <v>0.1808</v>
+      </c>
+      <c r="I30" s="20">
+        <v>3.9776</v>
+      </c>
+      <c r="J30" s="20">
+        <v>0</v>
+      </c>
+      <c r="K30" s="20">
+        <v>0</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O30" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P30" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R30" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S30" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T30" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U30" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V30" s="20"/>
       <c r="W30" s="20"/>
       <c r="X30" s="20"/>
@@ -2708,27 +3416,69 @@
       <c r="AF30" s="20"/>
     </row>
     <row r="31" s="4" customFormat="1">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="86"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
+      <c r="A31" s="5">
+        <v>20</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20">
+        <v>0.1647</v>
+      </c>
+      <c r="I31" s="20">
+        <v>0.1647</v>
+      </c>
+      <c r="J31" s="20">
+        <v>0</v>
+      </c>
+      <c r="K31" s="20">
+        <v>0</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O31" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P31" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q31" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R31" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S31" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T31" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U31" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V31" s="20"/>
       <c r="W31" s="20"/>
       <c r="X31" s="20"/>
@@ -2742,27 +3492,69 @@
       <c r="AF31" s="20"/>
     </row>
     <row r="32" s="4" customFormat="1">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="86"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="T32" s="20"/>
-      <c r="U32" s="20"/>
+      <c r="A32" s="5">
+        <v>21</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" s="5">
+        <v>58563</v>
+      </c>
+      <c r="H32" s="5">
+        <v>0.1308</v>
+      </c>
+      <c r="I32" s="5">
+        <v>7660.0404</v>
+      </c>
+      <c r="J32" s="5">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N32" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O32" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P32" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R32" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T32" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U32" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V32" s="20"/>
       <c r="W32" s="20"/>
       <c r="X32" s="20"/>
@@ -2776,27 +3568,69 @@
       <c r="AF32" s="20"/>
     </row>
     <row r="33" s="4" customFormat="1">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="20"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="86"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="20"/>
-      <c r="R33" s="20"/>
-      <c r="S33" s="20"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="20"/>
+      <c r="A33" s="5">
+        <v>22</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="5">
+        <v>3349</v>
+      </c>
+      <c r="H33" s="5">
+        <v>0.1341</v>
+      </c>
+      <c r="I33" s="5">
+        <v>449.1009</v>
+      </c>
+      <c r="J33" s="5">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O33" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P33" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R33" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T33" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U33" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V33" s="20"/>
       <c r="W33" s="20"/>
       <c r="X33" s="20"/>
@@ -2810,27 +3644,69 @@
       <c r="AF33" s="20"/>
     </row>
     <row r="34" s="4" customFormat="1">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="86"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="T34" s="20"/>
-      <c r="U34" s="20"/>
+      <c r="A34" s="5">
+        <v>23</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0.0356</v>
+      </c>
+      <c r="I34" s="5">
+        <v>0.0356</v>
+      </c>
+      <c r="J34" s="5">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O34" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P34" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R34" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S34" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T34" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U34" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V34" s="20"/>
       <c r="W34" s="20"/>
       <c r="X34" s="20"/>
@@ -2844,27 +3720,69 @@
       <c r="AF34" s="20"/>
     </row>
     <row r="35" s="4" customFormat="1">
-      <c r="A35" s="89"/>
-      <c r="B35" s="89"/>
-      <c r="C35" s="89"/>
-      <c r="D35" s="89"/>
-      <c r="E35" s="89"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="92"/>
-      <c r="I35" s="93"/>
-      <c r="J35" s="93"/>
-      <c r="K35" s="94"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="20"/>
-      <c r="R35" s="20"/>
-      <c r="S35" s="20"/>
-      <c r="T35" s="20"/>
-      <c r="U35" s="20"/>
+      <c r="A35" s="89">
+        <v>24</v>
+      </c>
+      <c r="B35" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="89" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="89" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="F35" s="90" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="91">
+        <v>2238</v>
+      </c>
+      <c r="H35" s="92">
+        <v>0.3147</v>
+      </c>
+      <c r="I35" s="93">
+        <v>704.2986</v>
+      </c>
+      <c r="J35" s="93">
+        <v>0</v>
+      </c>
+      <c r="K35" s="94">
+        <v>0</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N35" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O35" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P35" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R35" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T35" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U35" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V35" s="20"/>
       <c r="W35" s="20"/>
       <c r="X35" s="20"/>
@@ -2878,27 +3796,69 @@
       <c r="AF35" s="20"/>
     </row>
     <row r="36" s="4" customFormat="1">
-      <c r="A36" s="89"/>
-      <c r="B36" s="89"/>
-      <c r="C36" s="89"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="90"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="92"/>
-      <c r="I36" s="93"/>
-      <c r="J36" s="93"/>
-      <c r="K36" s="94"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="20"/>
-      <c r="O36" s="86"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="20"/>
-      <c r="R36" s="20"/>
-      <c r="S36" s="20"/>
-      <c r="T36" s="20"/>
-      <c r="U36" s="20"/>
+      <c r="A36" s="89">
+        <v>25</v>
+      </c>
+      <c r="B36" s="89" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="89" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="89" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="89" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="90" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" s="91">
+        <v>392</v>
+      </c>
+      <c r="H36" s="92">
+        <v>0.626</v>
+      </c>
+      <c r="I36" s="93">
+        <v>245.392</v>
+      </c>
+      <c r="J36" s="93">
+        <v>0</v>
+      </c>
+      <c r="K36" s="94">
+        <v>0</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N36" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O36" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P36" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q36" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R36" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S36" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T36" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U36" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V36" s="20"/>
       <c r="W36" s="20"/>
       <c r="X36" s="20"/>
@@ -2912,27 +3872,69 @@
       <c r="AF36" s="20"/>
     </row>
     <row r="37" s="4" customFormat="1">
-      <c r="A37" s="95"/>
-      <c r="B37" s="95"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="96"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="86"/>
-      <c r="P37" s="20"/>
-      <c r="Q37" s="20"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
-      <c r="T37" s="20"/>
-      <c r="U37" s="20"/>
+      <c r="A37" s="95">
+        <v>26</v>
+      </c>
+      <c r="B37" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="20">
+        <v>108</v>
+      </c>
+      <c r="H37" s="96">
+        <v>0.741</v>
+      </c>
+      <c r="I37" s="20">
+        <v>80.028</v>
+      </c>
+      <c r="J37" s="20">
+        <v>0</v>
+      </c>
+      <c r="K37" s="20">
+        <v>0</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N37" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O37" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P37" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q37" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R37" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S37" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T37" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U37" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V37" s="20"/>
       <c r="W37" s="20"/>
       <c r="X37" s="20"/>
@@ -2946,27 +3948,69 @@
       <c r="AF37" s="20"/>
     </row>
     <row r="38" s="4" customFormat="1">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="92"/>
-      <c r="J38" s="92"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="86"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
+      <c r="A38" s="7">
+        <v>27</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="20">
+        <v>47680</v>
+      </c>
+      <c r="H38" s="20">
+        <v>0.1617</v>
+      </c>
+      <c r="I38" s="92">
+        <v>7709.856</v>
+      </c>
+      <c r="J38" s="92">
+        <v>0</v>
+      </c>
+      <c r="K38" s="97">
+        <v>0</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="N38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="O38" s="86" t="s">
+        <v>72</v>
+      </c>
+      <c r="P38" s="20">
+        <v>11</v>
+      </c>
+      <c r="Q38" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="R38" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S38" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T38" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="U38" s="20" t="s">
+        <v>77</v>
+      </c>
       <c r="V38" s="20"/>
       <c r="W38" s="20"/>
       <c r="X38" s="20"/>
@@ -2980,27 +4024,69 @@
       <c r="AF38" s="20"/>
     </row>
     <row r="39">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
-      <c r="D39" s="85"/>
-      <c r="E39" s="85"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="85"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="85"/>
-      <c r="K39" s="85"/>
-      <c r="L39" s="85"/>
-      <c r="M39" s="85"/>
-      <c r="N39" s="85"/>
-      <c r="O39" s="98"/>
-      <c r="P39" s="85"/>
-      <c r="Q39" s="85"/>
-      <c r="R39" s="85"/>
-      <c r="S39" s="85"/>
-      <c r="T39" s="85"/>
-      <c r="U39" s="85"/>
+      <c r="A39" s="85">
+        <v>28</v>
+      </c>
+      <c r="B39" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D39" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E39" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F39" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="85">
+        <v>2530</v>
+      </c>
+      <c r="H39" s="85">
+        <v>0.294</v>
+      </c>
+      <c r="I39" s="85">
+        <v>743.82</v>
+      </c>
+      <c r="J39" s="85">
+        <v>0</v>
+      </c>
+      <c r="K39" s="85">
+        <v>0</v>
+      </c>
+      <c r="L39" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M39" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N39" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O39" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P39" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q39" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R39" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S39" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T39" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U39" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V39" s="85"/>
       <c r="W39" s="85"/>
       <c r="X39" s="85"/>
@@ -3014,27 +4100,69 @@
       <c r="AF39" s="85"/>
     </row>
     <row r="40">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="85"/>
-      <c r="D40" s="85"/>
-      <c r="E40" s="85"/>
-      <c r="F40" s="85"/>
-      <c r="G40" s="85"/>
-      <c r="H40" s="85"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="85"/>
-      <c r="M40" s="85"/>
-      <c r="N40" s="85"/>
-      <c r="O40" s="98"/>
-      <c r="P40" s="85"/>
-      <c r="Q40" s="85"/>
-      <c r="R40" s="85"/>
-      <c r="S40" s="85"/>
-      <c r="T40" s="85"/>
-      <c r="U40" s="85"/>
+      <c r="A40" s="85">
+        <v>29</v>
+      </c>
+      <c r="B40" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E40" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="G40" s="85">
+        <v>1886</v>
+      </c>
+      <c r="H40" s="85">
+        <v>0.29537</v>
+      </c>
+      <c r="I40" s="85">
+        <v>557.06782</v>
+      </c>
+      <c r="J40" s="85">
+        <v>0</v>
+      </c>
+      <c r="K40" s="85">
+        <v>0</v>
+      </c>
+      <c r="L40" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M40" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N40" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O40" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P40" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q40" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R40" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S40" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T40" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U40" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V40" s="85"/>
       <c r="W40" s="85"/>
       <c r="X40" s="85"/>
@@ -3048,27 +4176,69 @@
       <c r="AF40" s="85"/>
     </row>
     <row r="41">
-      <c r="A41" s="85"/>
-      <c r="B41" s="85"/>
-      <c r="C41" s="85"/>
-      <c r="D41" s="85"/>
-      <c r="E41" s="85"/>
-      <c r="F41" s="85"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="85"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="85"/>
-      <c r="K41" s="85"/>
-      <c r="L41" s="85"/>
-      <c r="M41" s="85"/>
-      <c r="N41" s="85"/>
-      <c r="O41" s="98"/>
-      <c r="P41" s="85"/>
-      <c r="Q41" s="85"/>
-      <c r="R41" s="85"/>
-      <c r="S41" s="85"/>
-      <c r="T41" s="85"/>
-      <c r="U41" s="85"/>
+      <c r="A41" s="85">
+        <v>30</v>
+      </c>
+      <c r="B41" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D41" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E41" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F41" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="85">
+        <v>1497</v>
+      </c>
+      <c r="H41" s="85">
+        <v>0.378</v>
+      </c>
+      <c r="I41" s="85">
+        <v>565.866</v>
+      </c>
+      <c r="J41" s="85">
+        <v>0</v>
+      </c>
+      <c r="K41" s="85">
+        <v>0</v>
+      </c>
+      <c r="L41" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M41" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N41" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O41" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P41" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q41" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R41" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S41" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T41" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U41" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V41" s="85"/>
       <c r="W41" s="85"/>
       <c r="X41" s="85"/>
@@ -3082,27 +4252,69 @@
       <c r="AF41" s="85"/>
     </row>
     <row r="42">
-      <c r="A42" s="85"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="85"/>
-      <c r="K42" s="85"/>
-      <c r="L42" s="85"/>
-      <c r="M42" s="85"/>
-      <c r="N42" s="85"/>
-      <c r="O42" s="98"/>
-      <c r="P42" s="85"/>
-      <c r="Q42" s="85"/>
-      <c r="R42" s="85"/>
-      <c r="S42" s="85"/>
-      <c r="T42" s="85"/>
-      <c r="U42" s="85"/>
+      <c r="A42" s="85">
+        <v>31</v>
+      </c>
+      <c r="B42" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D42" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E42" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F42" s="85" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="85">
+        <v>807</v>
+      </c>
+      <c r="H42" s="85">
+        <v>0.29537</v>
+      </c>
+      <c r="I42" s="85">
+        <v>238.36359</v>
+      </c>
+      <c r="J42" s="85">
+        <v>0</v>
+      </c>
+      <c r="K42" s="85">
+        <v>0</v>
+      </c>
+      <c r="L42" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M42" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N42" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O42" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P42" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q42" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R42" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S42" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T42" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U42" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V42" s="85"/>
       <c r="W42" s="85"/>
       <c r="X42" s="85"/>
@@ -3116,27 +4328,69 @@
       <c r="AF42" s="85"/>
     </row>
     <row r="43">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
-      <c r="D43" s="85"/>
-      <c r="E43" s="85"/>
-      <c r="F43" s="85"/>
-      <c r="G43" s="85"/>
-      <c r="H43" s="85"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="85"/>
-      <c r="K43" s="85"/>
-      <c r="L43" s="85"/>
-      <c r="M43" s="85"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="98"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-      <c r="R43" s="85"/>
-      <c r="S43" s="85"/>
-      <c r="T43" s="85"/>
-      <c r="U43" s="85"/>
+      <c r="A43" s="85">
+        <v>32</v>
+      </c>
+      <c r="B43" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D43" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E43" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F43" s="85" t="s">
+        <v>108</v>
+      </c>
+      <c r="G43" s="85">
+        <v>2400</v>
+      </c>
+      <c r="H43" s="85">
+        <v>0.0737</v>
+      </c>
+      <c r="I43" s="85">
+        <v>176.88</v>
+      </c>
+      <c r="J43" s="85">
+        <v>0</v>
+      </c>
+      <c r="K43" s="85">
+        <v>0</v>
+      </c>
+      <c r="L43" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M43" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N43" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O43" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P43" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q43" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R43" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T43" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U43" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V43" s="85"/>
       <c r="W43" s="85"/>
       <c r="X43" s="85"/>
@@ -3150,27 +4404,69 @@
       <c r="AF43" s="85"/>
     </row>
     <row r="44">
-      <c r="A44" s="85"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="85"/>
-      <c r="D44" s="85"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="85"/>
-      <c r="G44" s="85"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="85"/>
-      <c r="J44" s="85"/>
-      <c r="K44" s="85"/>
-      <c r="L44" s="85"/>
-      <c r="M44" s="85"/>
-      <c r="N44" s="85"/>
-      <c r="O44" s="98"/>
-      <c r="P44" s="85"/>
-      <c r="Q44" s="85"/>
-      <c r="R44" s="85"/>
-      <c r="S44" s="85"/>
-      <c r="T44" s="85"/>
-      <c r="U44" s="85"/>
+      <c r="A44" s="85">
+        <v>33</v>
+      </c>
+      <c r="B44" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D44" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F44" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="G44" s="85">
+        <v>1256</v>
+      </c>
+      <c r="H44" s="85">
+        <v>0.001</v>
+      </c>
+      <c r="I44" s="85">
+        <v>1.256</v>
+      </c>
+      <c r="J44" s="85">
+        <v>0</v>
+      </c>
+      <c r="K44" s="85">
+        <v>0</v>
+      </c>
+      <c r="L44" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M44" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N44" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O44" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P44" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q44" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R44" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T44" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U44" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V44" s="85"/>
       <c r="W44" s="85"/>
       <c r="X44" s="85"/>
@@ -3184,27 +4480,69 @@
       <c r="AF44" s="85"/>
     </row>
     <row r="45">
-      <c r="A45" s="85"/>
-      <c r="B45" s="85"/>
-      <c r="C45" s="85"/>
-      <c r="D45" s="85"/>
-      <c r="E45" s="85"/>
-      <c r="F45" s="85"/>
-      <c r="G45" s="85"/>
-      <c r="H45" s="85"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="85"/>
-      <c r="L45" s="85"/>
-      <c r="M45" s="85"/>
-      <c r="N45" s="85"/>
-      <c r="O45" s="98"/>
-      <c r="P45" s="85"/>
-      <c r="Q45" s="85"/>
-      <c r="R45" s="85"/>
-      <c r="S45" s="85"/>
-      <c r="T45" s="85"/>
-      <c r="U45" s="85"/>
+      <c r="A45" s="85">
+        <v>34</v>
+      </c>
+      <c r="B45" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C45" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D45" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E45" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F45" s="85" t="s">
+        <v>110</v>
+      </c>
+      <c r="G45" s="85">
+        <v>40690</v>
+      </c>
+      <c r="H45" s="85">
+        <v>0.0013</v>
+      </c>
+      <c r="I45" s="85">
+        <v>52.897</v>
+      </c>
+      <c r="J45" s="85">
+        <v>0</v>
+      </c>
+      <c r="K45" s="85">
+        <v>0</v>
+      </c>
+      <c r="L45" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M45" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N45" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O45" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P45" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q45" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R45" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S45" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T45" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U45" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V45" s="85"/>
       <c r="W45" s="85"/>
       <c r="X45" s="85"/>
@@ -3218,27 +4556,69 @@
       <c r="AF45" s="85"/>
     </row>
     <row r="46">
-      <c r="A46" s="85"/>
-      <c r="B46" s="85"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85"/>
-      <c r="F46" s="85"/>
-      <c r="G46" s="85"/>
-      <c r="H46" s="85"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="85"/>
-      <c r="K46" s="85"/>
-      <c r="L46" s="85"/>
-      <c r="M46" s="85"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="98"/>
-      <c r="P46" s="85"/>
-      <c r="Q46" s="85"/>
-      <c r="R46" s="85"/>
-      <c r="S46" s="85"/>
-      <c r="T46" s="85"/>
-      <c r="U46" s="85"/>
+      <c r="A46" s="85">
+        <v>35</v>
+      </c>
+      <c r="B46" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E46" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F46" s="85" t="s">
+        <v>111</v>
+      </c>
+      <c r="G46" s="85">
+        <v>7232</v>
+      </c>
+      <c r="H46" s="85">
+        <v>0.0013</v>
+      </c>
+      <c r="I46" s="85">
+        <v>9.4016</v>
+      </c>
+      <c r="J46" s="85">
+        <v>0</v>
+      </c>
+      <c r="K46" s="85">
+        <v>0</v>
+      </c>
+      <c r="L46" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M46" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N46" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O46" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P46" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q46" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R46" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S46" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T46" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U46" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V46" s="85"/>
       <c r="W46" s="85"/>
       <c r="X46" s="85"/>
@@ -3252,27 +4632,69 @@
       <c r="AF46" s="85"/>
     </row>
     <row r="47">
-      <c r="A47" s="85"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="85"/>
-      <c r="F47" s="85"/>
-      <c r="G47" s="85"/>
-      <c r="H47" s="85"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="85"/>
-      <c r="K47" s="85"/>
-      <c r="L47" s="85"/>
-      <c r="M47" s="85"/>
-      <c r="N47" s="85"/>
-      <c r="O47" s="98"/>
-      <c r="P47" s="85"/>
-      <c r="Q47" s="85"/>
-      <c r="R47" s="85"/>
-      <c r="S47" s="85"/>
-      <c r="T47" s="85"/>
-      <c r="U47" s="85"/>
+      <c r="A47" s="85">
+        <v>36</v>
+      </c>
+      <c r="B47" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E47" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F47" s="85" t="s">
+        <v>112</v>
+      </c>
+      <c r="G47" s="85">
+        <v>6863</v>
+      </c>
+      <c r="H47" s="85">
+        <v>0.0013</v>
+      </c>
+      <c r="I47" s="85">
+        <v>8.9219</v>
+      </c>
+      <c r="J47" s="85">
+        <v>0</v>
+      </c>
+      <c r="K47" s="85">
+        <v>0</v>
+      </c>
+      <c r="L47" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M47" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N47" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O47" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P47" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q47" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R47" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S47" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T47" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U47" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V47" s="85"/>
       <c r="W47" s="85"/>
       <c r="X47" s="85"/>
@@ -3286,27 +4708,69 @@
       <c r="AF47" s="85"/>
     </row>
     <row r="48">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="85"/>
-      <c r="F48" s="85"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="85"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
-      <c r="K48" s="85"/>
-      <c r="L48" s="85"/>
-      <c r="M48" s="85"/>
-      <c r="N48" s="85"/>
-      <c r="O48" s="98"/>
-      <c r="P48" s="85"/>
-      <c r="Q48" s="85"/>
-      <c r="R48" s="85"/>
-      <c r="S48" s="85"/>
-      <c r="T48" s="85"/>
-      <c r="U48" s="85"/>
+      <c r="A48" s="85">
+        <v>37</v>
+      </c>
+      <c r="B48" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E48" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F48" s="85" t="s">
+        <v>113</v>
+      </c>
+      <c r="G48" s="85">
+        <v>2701</v>
+      </c>
+      <c r="H48" s="85">
+        <v>0.0013</v>
+      </c>
+      <c r="I48" s="85">
+        <v>3.5113</v>
+      </c>
+      <c r="J48" s="85">
+        <v>0</v>
+      </c>
+      <c r="K48" s="85">
+        <v>0</v>
+      </c>
+      <c r="L48" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M48" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N48" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O48" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P48" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q48" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R48" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S48" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T48" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U48" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V48" s="85"/>
       <c r="W48" s="85"/>
       <c r="X48" s="85"/>
@@ -3320,27 +4784,69 @@
       <c r="AF48" s="85"/>
     </row>
     <row r="49">
-      <c r="A49" s="85"/>
-      <c r="B49" s="85"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="85"/>
-      <c r="F49" s="85"/>
-      <c r="G49" s="85"/>
-      <c r="H49" s="85"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="85"/>
-      <c r="K49" s="85"/>
-      <c r="L49" s="85"/>
-      <c r="M49" s="85"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="98"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-      <c r="R49" s="85"/>
-      <c r="S49" s="85"/>
-      <c r="T49" s="85"/>
-      <c r="U49" s="85"/>
+      <c r="A49" s="85">
+        <v>38</v>
+      </c>
+      <c r="B49" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D49" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" s="85">
+        <v>553</v>
+      </c>
+      <c r="H49" s="85">
+        <v>0.0013</v>
+      </c>
+      <c r="I49" s="85">
+        <v>0.7189</v>
+      </c>
+      <c r="J49" s="85">
+        <v>0</v>
+      </c>
+      <c r="K49" s="85">
+        <v>0</v>
+      </c>
+      <c r="L49" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M49" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N49" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P49" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q49" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R49" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S49" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T49" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U49" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V49" s="85"/>
       <c r="W49" s="85"/>
       <c r="X49" s="85"/>
@@ -3354,27 +4860,69 @@
       <c r="AF49" s="85"/>
     </row>
     <row r="50">
-      <c r="A50" s="85"/>
-      <c r="B50" s="85"/>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="85"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="85"/>
-      <c r="L50" s="85"/>
-      <c r="M50" s="85"/>
-      <c r="N50" s="85"/>
-      <c r="O50" s="98"/>
-      <c r="P50" s="85"/>
-      <c r="Q50" s="85"/>
-      <c r="R50" s="85"/>
-      <c r="S50" s="85"/>
-      <c r="T50" s="85"/>
-      <c r="U50" s="85"/>
+      <c r="A50" s="85">
+        <v>39</v>
+      </c>
+      <c r="B50" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D50" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F50" s="85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G50" s="85">
+        <v>31324</v>
+      </c>
+      <c r="H50" s="85">
+        <v>0.02</v>
+      </c>
+      <c r="I50" s="85">
+        <v>626.48</v>
+      </c>
+      <c r="J50" s="85">
+        <v>0</v>
+      </c>
+      <c r="K50" s="85">
+        <v>0</v>
+      </c>
+      <c r="L50" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M50" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N50" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O50" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P50" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q50" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R50" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S50" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T50" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U50" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V50" s="85"/>
       <c r="W50" s="85"/>
       <c r="X50" s="85"/>
@@ -3388,27 +4936,69 @@
       <c r="AF50" s="85"/>
     </row>
     <row r="51">
-      <c r="A51" s="85"/>
-      <c r="B51" s="85"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="85"/>
-      <c r="E51" s="85"/>
-      <c r="F51" s="85"/>
-      <c r="G51" s="85"/>
-      <c r="H51" s="85"/>
-      <c r="I51" s="85"/>
-      <c r="J51" s="85"/>
-      <c r="K51" s="85"/>
-      <c r="L51" s="85"/>
-      <c r="M51" s="85"/>
-      <c r="N51" s="85"/>
-      <c r="O51" s="98"/>
-      <c r="P51" s="85"/>
-      <c r="Q51" s="85"/>
-      <c r="R51" s="85"/>
-      <c r="S51" s="85"/>
-      <c r="T51" s="85"/>
-      <c r="U51" s="85"/>
+      <c r="A51" s="85">
+        <v>40</v>
+      </c>
+      <c r="B51" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D51" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F51" s="85" t="s">
+        <v>116</v>
+      </c>
+      <c r="G51" s="85">
+        <v>11685</v>
+      </c>
+      <c r="H51" s="85">
+        <v>0.0087</v>
+      </c>
+      <c r="I51" s="85">
+        <v>101.6595</v>
+      </c>
+      <c r="J51" s="85">
+        <v>0</v>
+      </c>
+      <c r="K51" s="85">
+        <v>0</v>
+      </c>
+      <c r="L51" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M51" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N51" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O51" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P51" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q51" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R51" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S51" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T51" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U51" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V51" s="85"/>
       <c r="W51" s="85"/>
       <c r="X51" s="85"/>
@@ -3422,27 +5012,69 @@
       <c r="AF51" s="85"/>
     </row>
     <row r="52">
-      <c r="A52" s="85"/>
-      <c r="B52" s="85"/>
-      <c r="C52" s="85"/>
-      <c r="D52" s="85"/>
-      <c r="E52" s="85"/>
-      <c r="F52" s="85"/>
-      <c r="G52" s="85"/>
-      <c r="H52" s="85"/>
-      <c r="I52" s="85"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="85"/>
-      <c r="L52" s="85"/>
-      <c r="M52" s="85"/>
-      <c r="N52" s="85"/>
-      <c r="O52" s="98"/>
-      <c r="P52" s="85"/>
-      <c r="Q52" s="85"/>
-      <c r="R52" s="85"/>
-      <c r="S52" s="85"/>
-      <c r="T52" s="85"/>
-      <c r="U52" s="85"/>
+      <c r="A52" s="85">
+        <v>41</v>
+      </c>
+      <c r="B52" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D52" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" s="85" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="85">
+        <v>3954</v>
+      </c>
+      <c r="H52" s="85">
+        <v>0.0083</v>
+      </c>
+      <c r="I52" s="85">
+        <v>32.8182</v>
+      </c>
+      <c r="J52" s="85">
+        <v>0</v>
+      </c>
+      <c r="K52" s="85">
+        <v>0</v>
+      </c>
+      <c r="L52" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M52" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N52" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O52" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P52" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q52" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R52" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S52" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T52" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U52" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V52" s="85"/>
       <c r="W52" s="85"/>
       <c r="X52" s="85"/>
@@ -3456,27 +5088,69 @@
       <c r="AF52" s="85"/>
     </row>
     <row r="53">
-      <c r="A53" s="85"/>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="85"/>
-      <c r="E53" s="85"/>
-      <c r="F53" s="85"/>
-      <c r="G53" s="85"/>
-      <c r="H53" s="85"/>
-      <c r="I53" s="85"/>
-      <c r="J53" s="85"/>
-      <c r="K53" s="85"/>
-      <c r="L53" s="85"/>
-      <c r="M53" s="85"/>
-      <c r="N53" s="85"/>
-      <c r="O53" s="98"/>
-      <c r="P53" s="85"/>
-      <c r="Q53" s="85"/>
-      <c r="R53" s="85"/>
-      <c r="S53" s="85"/>
-      <c r="T53" s="85"/>
-      <c r="U53" s="85"/>
+      <c r="A53" s="85">
+        <v>42</v>
+      </c>
+      <c r="B53" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F53" s="85" t="s">
+        <v>118</v>
+      </c>
+      <c r="G53" s="85">
+        <v>10621</v>
+      </c>
+      <c r="H53" s="85">
+        <v>0.0045</v>
+      </c>
+      <c r="I53" s="85">
+        <v>47.7945</v>
+      </c>
+      <c r="J53" s="85">
+        <v>0</v>
+      </c>
+      <c r="K53" s="85">
+        <v>0</v>
+      </c>
+      <c r="L53" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M53" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N53" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O53" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P53" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q53" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R53" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S53" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T53" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U53" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V53" s="85"/>
       <c r="W53" s="85"/>
       <c r="X53" s="85"/>
@@ -3490,27 +5164,69 @@
       <c r="AF53" s="85"/>
     </row>
     <row r="54">
-      <c r="A54" s="85"/>
-      <c r="B54" s="85"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="85"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="85"/>
-      <c r="L54" s="85"/>
-      <c r="M54" s="85"/>
-      <c r="N54" s="85"/>
-      <c r="O54" s="98"/>
-      <c r="P54" s="85"/>
-      <c r="Q54" s="85"/>
-      <c r="R54" s="85"/>
-      <c r="S54" s="85"/>
-      <c r="T54" s="85"/>
-      <c r="U54" s="85"/>
+      <c r="A54" s="85">
+        <v>43</v>
+      </c>
+      <c r="B54" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F54" s="85" t="s">
+        <v>119</v>
+      </c>
+      <c r="G54" s="85">
+        <v>528</v>
+      </c>
+      <c r="H54" s="85">
+        <v>0.015</v>
+      </c>
+      <c r="I54" s="85">
+        <v>7.92</v>
+      </c>
+      <c r="J54" s="85">
+        <v>0</v>
+      </c>
+      <c r="K54" s="85">
+        <v>0</v>
+      </c>
+      <c r="L54" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M54" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N54" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O54" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P54" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q54" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R54" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S54" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T54" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U54" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V54" s="85"/>
       <c r="W54" s="85"/>
       <c r="X54" s="85"/>
@@ -3524,27 +5240,69 @@
       <c r="AF54" s="85"/>
     </row>
     <row r="55">
-      <c r="A55" s="85"/>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
-      <c r="H55" s="85"/>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="85"/>
-      <c r="L55" s="85"/>
-      <c r="M55" s="85"/>
-      <c r="N55" s="85"/>
-      <c r="O55" s="98"/>
-      <c r="P55" s="85"/>
-      <c r="Q55" s="85"/>
-      <c r="R55" s="85"/>
-      <c r="S55" s="85"/>
-      <c r="T55" s="85"/>
-      <c r="U55" s="85"/>
+      <c r="A55" s="85">
+        <v>44</v>
+      </c>
+      <c r="B55" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="85" t="s">
+        <v>120</v>
+      </c>
+      <c r="G55" s="85">
+        <v>61962</v>
+      </c>
+      <c r="H55" s="85">
+        <v>0.0098</v>
+      </c>
+      <c r="I55" s="85">
+        <v>607.2276</v>
+      </c>
+      <c r="J55" s="85">
+        <v>0</v>
+      </c>
+      <c r="K55" s="85">
+        <v>0</v>
+      </c>
+      <c r="L55" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M55" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N55" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O55" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P55" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q55" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R55" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S55" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T55" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U55" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V55" s="85"/>
       <c r="W55" s="85"/>
       <c r="X55" s="85"/>
@@ -3558,27 +5316,69 @@
       <c r="AF55" s="85"/>
     </row>
     <row r="56">
-      <c r="A56" s="85"/>
-      <c r="B56" s="85"/>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
-      <c r="H56" s="85"/>
-      <c r="I56" s="85"/>
-      <c r="J56" s="85"/>
-      <c r="K56" s="85"/>
-      <c r="L56" s="85"/>
-      <c r="M56" s="85"/>
-      <c r="N56" s="85"/>
-      <c r="O56" s="98"/>
-      <c r="P56" s="85"/>
-      <c r="Q56" s="85"/>
-      <c r="R56" s="85"/>
-      <c r="S56" s="85"/>
-      <c r="T56" s="85"/>
-      <c r="U56" s="85"/>
+      <c r="A56" s="85">
+        <v>45</v>
+      </c>
+      <c r="B56" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D56" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F56" s="85" t="s">
+        <v>121</v>
+      </c>
+      <c r="G56" s="85">
+        <v>3527</v>
+      </c>
+      <c r="H56" s="85">
+        <v>0.0098</v>
+      </c>
+      <c r="I56" s="85">
+        <v>34.5646</v>
+      </c>
+      <c r="J56" s="85">
+        <v>0</v>
+      </c>
+      <c r="K56" s="85">
+        <v>0</v>
+      </c>
+      <c r="L56" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M56" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N56" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P56" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q56" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R56" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S56" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T56" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U56" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V56" s="85"/>
       <c r="W56" s="85"/>
       <c r="X56" s="85"/>
@@ -3592,27 +5392,69 @@
       <c r="AF56" s="85"/>
     </row>
     <row r="57">
-      <c r="A57" s="85"/>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="85"/>
-      <c r="L57" s="85"/>
-      <c r="M57" s="85"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="98"/>
-      <c r="P57" s="85"/>
-      <c r="Q57" s="85"/>
-      <c r="R57" s="85"/>
-      <c r="S57" s="85"/>
-      <c r="T57" s="85"/>
-      <c r="U57" s="85"/>
+      <c r="A57" s="85">
+        <v>46</v>
+      </c>
+      <c r="B57" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D57" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F57" s="85" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="85">
+        <v>2</v>
+      </c>
+      <c r="H57" s="85">
+        <v>0.04197</v>
+      </c>
+      <c r="I57" s="85">
+        <v>0.08394</v>
+      </c>
+      <c r="J57" s="85">
+        <v>0</v>
+      </c>
+      <c r="K57" s="85">
+        <v>0</v>
+      </c>
+      <c r="L57" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M57" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N57" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O57" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P57" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q57" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R57" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S57" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T57" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U57" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V57" s="85"/>
       <c r="W57" s="85"/>
       <c r="X57" s="85"/>
@@ -3626,27 +5468,69 @@
       <c r="AF57" s="85"/>
     </row>
     <row r="58">
-      <c r="A58" s="85"/>
-      <c r="B58" s="85"/>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="85"/>
-      <c r="F58" s="85"/>
-      <c r="G58" s="85"/>
-      <c r="H58" s="85"/>
-      <c r="I58" s="85"/>
-      <c r="J58" s="85"/>
-      <c r="K58" s="85"/>
-      <c r="L58" s="85"/>
-      <c r="M58" s="85"/>
-      <c r="N58" s="85"/>
-      <c r="O58" s="98"/>
-      <c r="P58" s="85"/>
-      <c r="Q58" s="85"/>
-      <c r="R58" s="85"/>
-      <c r="S58" s="85"/>
-      <c r="T58" s="85"/>
-      <c r="U58" s="85"/>
+      <c r="A58" s="85">
+        <v>47</v>
+      </c>
+      <c r="B58" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F58" s="85" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="85">
+        <v>2</v>
+      </c>
+      <c r="H58" s="85">
+        <v>0.03244</v>
+      </c>
+      <c r="I58" s="85">
+        <v>0.06488</v>
+      </c>
+      <c r="J58" s="85">
+        <v>0</v>
+      </c>
+      <c r="K58" s="85">
+        <v>0</v>
+      </c>
+      <c r="L58" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M58" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N58" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O58" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P58" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q58" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R58" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S58" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T58" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U58" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V58" s="85"/>
       <c r="W58" s="85"/>
       <c r="X58" s="85"/>
@@ -3660,27 +5544,69 @@
       <c r="AF58" s="85"/>
     </row>
     <row r="59">
-      <c r="A59" s="85"/>
-      <c r="B59" s="85"/>
-      <c r="C59" s="85"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="85"/>
-      <c r="F59" s="85"/>
-      <c r="G59" s="85"/>
-      <c r="H59" s="85"/>
-      <c r="I59" s="85"/>
-      <c r="J59" s="85"/>
-      <c r="K59" s="85"/>
-      <c r="L59" s="85"/>
-      <c r="M59" s="85"/>
-      <c r="N59" s="85"/>
-      <c r="O59" s="98"/>
-      <c r="P59" s="85"/>
-      <c r="Q59" s="85"/>
-      <c r="R59" s="85"/>
-      <c r="S59" s="85"/>
-      <c r="T59" s="85"/>
-      <c r="U59" s="85"/>
+      <c r="A59" s="85">
+        <v>48</v>
+      </c>
+      <c r="B59" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D59" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F59" s="85" t="s">
+        <v>124</v>
+      </c>
+      <c r="G59" s="85">
+        <v>4</v>
+      </c>
+      <c r="H59" s="85">
+        <v>0.03244</v>
+      </c>
+      <c r="I59" s="85">
+        <v>0.12976</v>
+      </c>
+      <c r="J59" s="85">
+        <v>0</v>
+      </c>
+      <c r="K59" s="85">
+        <v>0</v>
+      </c>
+      <c r="L59" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M59" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N59" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O59" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P59" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q59" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R59" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S59" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T59" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U59" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V59" s="85"/>
       <c r="W59" s="85"/>
       <c r="X59" s="85"/>
@@ -3694,27 +5620,69 @@
       <c r="AF59" s="85"/>
     </row>
     <row r="60">
-      <c r="A60" s="85"/>
-      <c r="B60" s="85"/>
-      <c r="C60" s="85"/>
-      <c r="D60" s="85"/>
-      <c r="E60" s="85"/>
-      <c r="F60" s="85"/>
-      <c r="G60" s="85"/>
-      <c r="H60" s="85"/>
-      <c r="I60" s="85"/>
-      <c r="J60" s="85"/>
-      <c r="K60" s="85"/>
-      <c r="L60" s="85"/>
-      <c r="M60" s="85"/>
-      <c r="N60" s="85"/>
-      <c r="O60" s="98"/>
-      <c r="P60" s="85"/>
-      <c r="Q60" s="85"/>
-      <c r="R60" s="85"/>
-      <c r="S60" s="85"/>
-      <c r="T60" s="85"/>
-      <c r="U60" s="85"/>
+      <c r="A60" s="85">
+        <v>49</v>
+      </c>
+      <c r="B60" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F60" s="85" t="s">
+        <v>125</v>
+      </c>
+      <c r="G60" s="85">
+        <v>9163</v>
+      </c>
+      <c r="H60" s="85">
+        <v>0.26553</v>
+      </c>
+      <c r="I60" s="85">
+        <v>2433.05139</v>
+      </c>
+      <c r="J60" s="85">
+        <v>0</v>
+      </c>
+      <c r="K60" s="85">
+        <v>0</v>
+      </c>
+      <c r="L60" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M60" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N60" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O60" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P60" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q60" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R60" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S60" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T60" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U60" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V60" s="85"/>
       <c r="W60" s="85"/>
       <c r="X60" s="85"/>
@@ -3728,27 +5696,69 @@
       <c r="AF60" s="85"/>
     </row>
     <row r="61">
-      <c r="A61" s="85"/>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
-      <c r="D61" s="85"/>
-      <c r="E61" s="85"/>
-      <c r="F61" s="85"/>
-      <c r="G61" s="85"/>
-      <c r="H61" s="85"/>
-      <c r="I61" s="85"/>
-      <c r="J61" s="85"/>
-      <c r="K61" s="85"/>
-      <c r="L61" s="85"/>
-      <c r="M61" s="85"/>
-      <c r="N61" s="85"/>
-      <c r="O61" s="98"/>
-      <c r="P61" s="85"/>
-      <c r="Q61" s="85"/>
-      <c r="R61" s="85"/>
-      <c r="S61" s="85"/>
-      <c r="T61" s="85"/>
-      <c r="U61" s="85"/>
+      <c r="A61" s="85">
+        <v>50</v>
+      </c>
+      <c r="B61" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D61" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F61" s="85" t="s">
+        <v>126</v>
+      </c>
+      <c r="G61" s="85">
+        <v>61915</v>
+      </c>
+      <c r="H61" s="85">
+        <v>0.00877</v>
+      </c>
+      <c r="I61" s="85">
+        <v>542.99455</v>
+      </c>
+      <c r="J61" s="85">
+        <v>0</v>
+      </c>
+      <c r="K61" s="85">
+        <v>0</v>
+      </c>
+      <c r="L61" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M61" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N61" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O61" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P61" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q61" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R61" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S61" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T61" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U61" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V61" s="85"/>
       <c r="W61" s="85"/>
       <c r="X61" s="85"/>
@@ -3762,27 +5772,69 @@
       <c r="AF61" s="85"/>
     </row>
     <row r="62">
-      <c r="A62" s="85"/>
-      <c r="B62" s="85"/>
-      <c r="C62" s="85"/>
-      <c r="D62" s="85"/>
-      <c r="E62" s="85"/>
-      <c r="F62" s="85"/>
-      <c r="G62" s="85"/>
-      <c r="H62" s="85"/>
-      <c r="I62" s="85"/>
-      <c r="J62" s="85"/>
-      <c r="K62" s="85"/>
-      <c r="L62" s="85"/>
-      <c r="M62" s="85"/>
-      <c r="N62" s="85"/>
-      <c r="O62" s="98"/>
-      <c r="P62" s="85"/>
-      <c r="Q62" s="85"/>
-      <c r="R62" s="85"/>
-      <c r="S62" s="85"/>
-      <c r="T62" s="85"/>
-      <c r="U62" s="85"/>
+      <c r="A62" s="85">
+        <v>51</v>
+      </c>
+      <c r="B62" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D62" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E62" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F62" s="85" t="s">
+        <v>127</v>
+      </c>
+      <c r="G62" s="85">
+        <v>61937</v>
+      </c>
+      <c r="H62" s="85">
+        <v>0.0132</v>
+      </c>
+      <c r="I62" s="85">
+        <v>817.5684</v>
+      </c>
+      <c r="J62" s="85">
+        <v>0</v>
+      </c>
+      <c r="K62" s="85">
+        <v>0</v>
+      </c>
+      <c r="L62" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M62" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N62" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O62" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P62" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q62" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R62" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S62" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T62" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U62" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V62" s="85"/>
       <c r="W62" s="85"/>
       <c r="X62" s="85"/>
@@ -3796,27 +5848,69 @@
       <c r="AF62" s="85"/>
     </row>
     <row r="63">
-      <c r="A63" s="85"/>
-      <c r="B63" s="85"/>
-      <c r="C63" s="85"/>
-      <c r="D63" s="85"/>
-      <c r="E63" s="85"/>
-      <c r="F63" s="85"/>
-      <c r="G63" s="85"/>
-      <c r="H63" s="85"/>
-      <c r="I63" s="85"/>
-      <c r="J63" s="85"/>
-      <c r="K63" s="85"/>
-      <c r="L63" s="85"/>
-      <c r="M63" s="85"/>
-      <c r="N63" s="85"/>
-      <c r="O63" s="98"/>
-      <c r="P63" s="85"/>
-      <c r="Q63" s="85"/>
-      <c r="R63" s="85"/>
-      <c r="S63" s="85"/>
-      <c r="T63" s="85"/>
-      <c r="U63" s="85"/>
+      <c r="A63" s="85">
+        <v>52</v>
+      </c>
+      <c r="B63" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E63" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F63" s="85" t="s">
+        <v>128</v>
+      </c>
+      <c r="G63" s="85">
+        <v>84</v>
+      </c>
+      <c r="H63" s="85">
+        <v>0.1438</v>
+      </c>
+      <c r="I63" s="85">
+        <v>12.0792</v>
+      </c>
+      <c r="J63" s="85">
+        <v>0</v>
+      </c>
+      <c r="K63" s="85">
+        <v>0</v>
+      </c>
+      <c r="L63" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M63" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N63" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O63" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P63" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q63" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R63" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S63" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T63" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U63" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V63" s="85"/>
       <c r="W63" s="85"/>
       <c r="X63" s="85"/>
@@ -3830,27 +5924,69 @@
       <c r="AF63" s="85"/>
     </row>
     <row r="64">
-      <c r="A64" s="85"/>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
-      <c r="D64" s="85"/>
-      <c r="E64" s="85"/>
-      <c r="F64" s="85"/>
-      <c r="G64" s="85"/>
-      <c r="H64" s="85"/>
-      <c r="I64" s="85"/>
-      <c r="J64" s="85"/>
-      <c r="K64" s="85"/>
-      <c r="L64" s="85"/>
-      <c r="M64" s="85"/>
-      <c r="N64" s="85"/>
-      <c r="O64" s="98"/>
-      <c r="P64" s="85"/>
-      <c r="Q64" s="85"/>
-      <c r="R64" s="85"/>
-      <c r="S64" s="85"/>
-      <c r="T64" s="85"/>
-      <c r="U64" s="85"/>
+      <c r="A64" s="85">
+        <v>53</v>
+      </c>
+      <c r="B64" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E64" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F64" s="85" t="s">
+        <v>129</v>
+      </c>
+      <c r="G64" s="85">
+        <v>2</v>
+      </c>
+      <c r="H64" s="85">
+        <v>0.1758</v>
+      </c>
+      <c r="I64" s="85">
+        <v>0.3516</v>
+      </c>
+      <c r="J64" s="85">
+        <v>0</v>
+      </c>
+      <c r="K64" s="85">
+        <v>0</v>
+      </c>
+      <c r="L64" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M64" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N64" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O64" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P64" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q64" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R64" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S64" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T64" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U64" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V64" s="85"/>
       <c r="W64" s="85"/>
       <c r="X64" s="85"/>
@@ -3864,27 +6000,69 @@
       <c r="AF64" s="85"/>
     </row>
     <row r="65">
-      <c r="A65" s="85"/>
-      <c r="B65" s="85"/>
-      <c r="C65" s="85"/>
-      <c r="D65" s="85"/>
-      <c r="E65" s="85"/>
-      <c r="F65" s="85"/>
-      <c r="G65" s="85"/>
-      <c r="H65" s="85"/>
-      <c r="I65" s="85"/>
-      <c r="J65" s="85"/>
-      <c r="K65" s="85"/>
-      <c r="L65" s="85"/>
-      <c r="M65" s="85"/>
-      <c r="N65" s="85"/>
-      <c r="O65" s="98"/>
-      <c r="P65" s="85"/>
-      <c r="Q65" s="85"/>
-      <c r="R65" s="85"/>
-      <c r="S65" s="85"/>
-      <c r="T65" s="85"/>
-      <c r="U65" s="85"/>
+      <c r="A65" s="85">
+        <v>54</v>
+      </c>
+      <c r="B65" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E65" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F65" s="85" t="s">
+        <v>130</v>
+      </c>
+      <c r="G65" s="85">
+        <v>12</v>
+      </c>
+      <c r="H65" s="85">
+        <v>0.2241</v>
+      </c>
+      <c r="I65" s="85">
+        <v>2.6892</v>
+      </c>
+      <c r="J65" s="85">
+        <v>0</v>
+      </c>
+      <c r="K65" s="85">
+        <v>0</v>
+      </c>
+      <c r="L65" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M65" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N65" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O65" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P65" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q65" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R65" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S65" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T65" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U65" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V65" s="85"/>
       <c r="W65" s="85"/>
       <c r="X65" s="85"/>
@@ -3898,27 +6076,69 @@
       <c r="AF65" s="85"/>
     </row>
     <row r="66">
-      <c r="A66" s="85"/>
-      <c r="B66" s="85"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="85"/>
-      <c r="E66" s="85"/>
-      <c r="F66" s="85"/>
-      <c r="G66" s="85"/>
-      <c r="H66" s="85"/>
-      <c r="I66" s="85"/>
-      <c r="J66" s="85"/>
-      <c r="K66" s="85"/>
-      <c r="L66" s="85"/>
-      <c r="M66" s="85"/>
-      <c r="N66" s="85"/>
-      <c r="O66" s="98"/>
-      <c r="P66" s="85"/>
-      <c r="Q66" s="85"/>
-      <c r="R66" s="85"/>
-      <c r="S66" s="85"/>
-      <c r="T66" s="85"/>
-      <c r="U66" s="85"/>
+      <c r="A66" s="85">
+        <v>55</v>
+      </c>
+      <c r="B66" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E66" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F66" s="85" t="s">
+        <v>131</v>
+      </c>
+      <c r="G66" s="85">
+        <v>13</v>
+      </c>
+      <c r="H66" s="85">
+        <v>0.185</v>
+      </c>
+      <c r="I66" s="85">
+        <v>2.405</v>
+      </c>
+      <c r="J66" s="85">
+        <v>0</v>
+      </c>
+      <c r="K66" s="85">
+        <v>0</v>
+      </c>
+      <c r="L66" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M66" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N66" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O66" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P66" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q66" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R66" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S66" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T66" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U66" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V66" s="85"/>
       <c r="W66" s="85"/>
       <c r="X66" s="85"/>
@@ -3932,27 +6152,69 @@
       <c r="AF66" s="85"/>
     </row>
     <row r="67">
-      <c r="A67" s="85"/>
-      <c r="B67" s="85"/>
-      <c r="C67" s="85"/>
-      <c r="D67" s="85"/>
-      <c r="E67" s="85"/>
-      <c r="F67" s="85"/>
-      <c r="G67" s="85"/>
-      <c r="H67" s="85"/>
-      <c r="I67" s="85"/>
-      <c r="J67" s="85"/>
-      <c r="K67" s="85"/>
-      <c r="L67" s="85"/>
-      <c r="M67" s="85"/>
-      <c r="N67" s="85"/>
-      <c r="O67" s="98"/>
-      <c r="P67" s="85"/>
-      <c r="Q67" s="85"/>
-      <c r="R67" s="85"/>
-      <c r="S67" s="85"/>
-      <c r="T67" s="85"/>
-      <c r="U67" s="85"/>
+      <c r="A67" s="85">
+        <v>56</v>
+      </c>
+      <c r="B67" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C67" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E67" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F67" s="85" t="s">
+        <v>132</v>
+      </c>
+      <c r="G67" s="85">
+        <v>2</v>
+      </c>
+      <c r="H67" s="85">
+        <v>0.2201</v>
+      </c>
+      <c r="I67" s="85">
+        <v>0.4402</v>
+      </c>
+      <c r="J67" s="85">
+        <v>0</v>
+      </c>
+      <c r="K67" s="85">
+        <v>0</v>
+      </c>
+      <c r="L67" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M67" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N67" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O67" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P67" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q67" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R67" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S67" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T67" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U67" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V67" s="85"/>
       <c r="W67" s="85"/>
       <c r="X67" s="85"/>
@@ -3966,27 +6228,69 @@
       <c r="AF67" s="85"/>
     </row>
     <row r="68">
-      <c r="A68" s="85"/>
-      <c r="B68" s="85"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="85"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="85"/>
-      <c r="I68" s="85"/>
-      <c r="J68" s="85"/>
-      <c r="K68" s="85"/>
-      <c r="L68" s="85"/>
-      <c r="M68" s="85"/>
-      <c r="N68" s="85"/>
-      <c r="O68" s="98"/>
-      <c r="P68" s="85"/>
-      <c r="Q68" s="85"/>
-      <c r="R68" s="85"/>
-      <c r="S68" s="85"/>
-      <c r="T68" s="85"/>
-      <c r="U68" s="85"/>
+      <c r="A68" s="85">
+        <v>57</v>
+      </c>
+      <c r="B68" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F68" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="G68" s="85">
+        <v>10050</v>
+      </c>
+      <c r="H68" s="85">
+        <v>0.1176</v>
+      </c>
+      <c r="I68" s="85">
+        <v>1181.88</v>
+      </c>
+      <c r="J68" s="85">
+        <v>0</v>
+      </c>
+      <c r="K68" s="85">
+        <v>0</v>
+      </c>
+      <c r="L68" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M68" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N68" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O68" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P68" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q68" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R68" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S68" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T68" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U68" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V68" s="85"/>
       <c r="W68" s="85"/>
       <c r="X68" s="85"/>
@@ -4000,27 +6304,69 @@
       <c r="AF68" s="85"/>
     </row>
     <row r="69">
-      <c r="A69" s="85"/>
-      <c r="B69" s="85"/>
-      <c r="C69" s="85"/>
-      <c r="D69" s="85"/>
-      <c r="E69" s="85"/>
-      <c r="F69" s="85"/>
-      <c r="G69" s="85"/>
-      <c r="H69" s="85"/>
-      <c r="I69" s="85"/>
-      <c r="J69" s="85"/>
-      <c r="K69" s="85"/>
-      <c r="L69" s="85"/>
-      <c r="M69" s="85"/>
-      <c r="N69" s="85"/>
-      <c r="O69" s="98"/>
-      <c r="P69" s="85"/>
-      <c r="Q69" s="85"/>
-      <c r="R69" s="85"/>
-      <c r="S69" s="85"/>
-      <c r="T69" s="85"/>
-      <c r="U69" s="85"/>
+      <c r="A69" s="85">
+        <v>58</v>
+      </c>
+      <c r="B69" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E69" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F69" s="85" t="s">
+        <v>134</v>
+      </c>
+      <c r="G69" s="85">
+        <v>17</v>
+      </c>
+      <c r="H69" s="85">
+        <v>18</v>
+      </c>
+      <c r="I69" s="85">
+        <v>306</v>
+      </c>
+      <c r="J69" s="85">
+        <v>0</v>
+      </c>
+      <c r="K69" s="85">
+        <v>0</v>
+      </c>
+      <c r="L69" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M69" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N69" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O69" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P69" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q69" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R69" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S69" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T69" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U69" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V69" s="85"/>
       <c r="W69" s="85"/>
       <c r="X69" s="85"/>
@@ -4034,27 +6380,69 @@
       <c r="AF69" s="85"/>
     </row>
     <row r="70">
-      <c r="A70" s="85"/>
-      <c r="B70" s="85"/>
-      <c r="C70" s="85"/>
-      <c r="D70" s="85"/>
-      <c r="E70" s="85"/>
-      <c r="F70" s="85"/>
-      <c r="G70" s="85"/>
-      <c r="H70" s="85"/>
-      <c r="I70" s="85"/>
-      <c r="J70" s="85"/>
-      <c r="K70" s="85"/>
-      <c r="L70" s="85"/>
-      <c r="M70" s="85"/>
-      <c r="N70" s="85"/>
-      <c r="O70" s="98"/>
-      <c r="P70" s="85"/>
-      <c r="Q70" s="85"/>
-      <c r="R70" s="85"/>
-      <c r="S70" s="85"/>
-      <c r="T70" s="85"/>
-      <c r="U70" s="85"/>
+      <c r="A70" s="85">
+        <v>59</v>
+      </c>
+      <c r="B70" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E70" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F70" s="85" t="s">
+        <v>135</v>
+      </c>
+      <c r="G70" s="85">
+        <v>103</v>
+      </c>
+      <c r="H70" s="85">
+        <v>0.0014</v>
+      </c>
+      <c r="I70" s="85">
+        <v>0.1442</v>
+      </c>
+      <c r="J70" s="85">
+        <v>0</v>
+      </c>
+      <c r="K70" s="85">
+        <v>0</v>
+      </c>
+      <c r="L70" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M70" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N70" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O70" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P70" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q70" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R70" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S70" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T70" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U70" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V70" s="85"/>
       <c r="W70" s="85"/>
       <c r="X70" s="85"/>
@@ -4068,27 +6456,69 @@
       <c r="AF70" s="85"/>
     </row>
     <row r="71">
-      <c r="A71" s="85"/>
-      <c r="B71" s="85"/>
-      <c r="C71" s="85"/>
-      <c r="D71" s="85"/>
-      <c r="E71" s="85"/>
-      <c r="F71" s="85"/>
-      <c r="G71" s="85"/>
-      <c r="H71" s="85"/>
-      <c r="I71" s="85"/>
-      <c r="J71" s="85"/>
-      <c r="K71" s="85"/>
-      <c r="L71" s="85"/>
-      <c r="M71" s="85"/>
-      <c r="N71" s="85"/>
-      <c r="O71" s="98"/>
-      <c r="P71" s="85"/>
-      <c r="Q71" s="85"/>
-      <c r="R71" s="85"/>
-      <c r="S71" s="85"/>
-      <c r="T71" s="85"/>
-      <c r="U71" s="85"/>
+      <c r="A71" s="85">
+        <v>60</v>
+      </c>
+      <c r="B71" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C71" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E71" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F71" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="G71" s="85">
+        <v>11</v>
+      </c>
+      <c r="H71" s="85">
+        <v>17.33</v>
+      </c>
+      <c r="I71" s="85">
+        <v>190.63</v>
+      </c>
+      <c r="J71" s="85">
+        <v>0</v>
+      </c>
+      <c r="K71" s="85">
+        <v>0</v>
+      </c>
+      <c r="L71" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M71" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N71" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O71" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P71" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q71" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R71" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S71" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T71" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U71" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V71" s="85"/>
       <c r="W71" s="85"/>
       <c r="X71" s="85"/>
@@ -4102,27 +6532,69 @@
       <c r="AF71" s="85"/>
     </row>
     <row r="72">
-      <c r="A72" s="85"/>
-      <c r="B72" s="85"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="85"/>
-      <c r="E72" s="85"/>
-      <c r="F72" s="85"/>
-      <c r="G72" s="85"/>
-      <c r="H72" s="85"/>
-      <c r="I72" s="85"/>
-      <c r="J72" s="85"/>
-      <c r="K72" s="85"/>
-      <c r="L72" s="85"/>
-      <c r="M72" s="85"/>
-      <c r="N72" s="85"/>
-      <c r="O72" s="98"/>
-      <c r="P72" s="85"/>
-      <c r="Q72" s="85"/>
-      <c r="R72" s="85"/>
-      <c r="S72" s="85"/>
-      <c r="T72" s="85"/>
-      <c r="U72" s="85"/>
+      <c r="A72" s="85">
+        <v>61</v>
+      </c>
+      <c r="B72" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E72" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F72" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="G72" s="85">
+        <v>7</v>
+      </c>
+      <c r="H72" s="85">
+        <v>51.2</v>
+      </c>
+      <c r="I72" s="85">
+        <v>358.4</v>
+      </c>
+      <c r="J72" s="85">
+        <v>0</v>
+      </c>
+      <c r="K72" s="85">
+        <v>0</v>
+      </c>
+      <c r="L72" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M72" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N72" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O72" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P72" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q72" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R72" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S72" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T72" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U72" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V72" s="85"/>
       <c r="W72" s="85"/>
       <c r="X72" s="85"/>
@@ -4136,27 +6608,69 @@
       <c r="AF72" s="85"/>
     </row>
     <row r="73">
-      <c r="A73" s="85"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85"/>
-      <c r="D73" s="85"/>
-      <c r="E73" s="85"/>
-      <c r="F73" s="85"/>
-      <c r="G73" s="85"/>
-      <c r="H73" s="85"/>
-      <c r="I73" s="85"/>
-      <c r="J73" s="85"/>
-      <c r="K73" s="85"/>
-      <c r="L73" s="85"/>
-      <c r="M73" s="85"/>
-      <c r="N73" s="85"/>
-      <c r="O73" s="98"/>
-      <c r="P73" s="85"/>
-      <c r="Q73" s="85"/>
-      <c r="R73" s="85"/>
-      <c r="S73" s="85"/>
-      <c r="T73" s="85"/>
-      <c r="U73" s="85"/>
+      <c r="A73" s="85">
+        <v>62</v>
+      </c>
+      <c r="B73" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E73" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F73" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="G73" s="85">
+        <v>20511</v>
+      </c>
+      <c r="H73" s="85">
+        <v>0.0069</v>
+      </c>
+      <c r="I73" s="85">
+        <v>141.5259</v>
+      </c>
+      <c r="J73" s="85">
+        <v>0</v>
+      </c>
+      <c r="K73" s="85">
+        <v>0</v>
+      </c>
+      <c r="L73" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M73" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N73" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O73" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P73" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q73" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R73" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S73" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T73" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U73" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V73" s="85"/>
       <c r="W73" s="85"/>
       <c r="X73" s="85"/>
@@ -4170,27 +6684,69 @@
       <c r="AF73" s="85"/>
     </row>
     <row r="74">
-      <c r="A74" s="85"/>
-      <c r="B74" s="85"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="85"/>
-      <c r="E74" s="85"/>
-      <c r="F74" s="85"/>
-      <c r="G74" s="85"/>
-      <c r="H74" s="85"/>
-      <c r="I74" s="85"/>
-      <c r="J74" s="85"/>
-      <c r="K74" s="85"/>
-      <c r="L74" s="85"/>
-      <c r="M74" s="85"/>
-      <c r="N74" s="85"/>
-      <c r="O74" s="98"/>
-      <c r="P74" s="85"/>
-      <c r="Q74" s="85"/>
-      <c r="R74" s="85"/>
-      <c r="S74" s="85"/>
-      <c r="T74" s="85"/>
-      <c r="U74" s="85"/>
+      <c r="A74" s="85">
+        <v>63</v>
+      </c>
+      <c r="B74" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C74" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E74" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F74" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="G74" s="85">
+        <v>14</v>
+      </c>
+      <c r="H74" s="85">
+        <v>12.7</v>
+      </c>
+      <c r="I74" s="85">
+        <v>177.8</v>
+      </c>
+      <c r="J74" s="85">
+        <v>0</v>
+      </c>
+      <c r="K74" s="85">
+        <v>0</v>
+      </c>
+      <c r="L74" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M74" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N74" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O74" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P74" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q74" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R74" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S74" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T74" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U74" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V74" s="85"/>
       <c r="W74" s="85"/>
       <c r="X74" s="85"/>
@@ -4204,27 +6760,69 @@
       <c r="AF74" s="85"/>
     </row>
     <row r="75">
-      <c r="A75" s="85"/>
-      <c r="B75" s="85"/>
-      <c r="C75" s="85"/>
-      <c r="D75" s="85"/>
-      <c r="E75" s="85"/>
-      <c r="F75" s="85"/>
-      <c r="G75" s="85"/>
-      <c r="H75" s="85"/>
-      <c r="I75" s="85"/>
-      <c r="J75" s="85"/>
-      <c r="K75" s="85"/>
-      <c r="L75" s="85"/>
-      <c r="M75" s="85"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="98"/>
-      <c r="P75" s="85"/>
-      <c r="Q75" s="85"/>
-      <c r="R75" s="85"/>
-      <c r="S75" s="85"/>
-      <c r="T75" s="85"/>
-      <c r="U75" s="85"/>
+      <c r="A75" s="85">
+        <v>64</v>
+      </c>
+      <c r="B75" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E75" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F75" s="85" t="s">
+        <v>140</v>
+      </c>
+      <c r="G75" s="85">
+        <v>19</v>
+      </c>
+      <c r="H75" s="85">
+        <v>3.63</v>
+      </c>
+      <c r="I75" s="85">
+        <v>68.97</v>
+      </c>
+      <c r="J75" s="85">
+        <v>0</v>
+      </c>
+      <c r="K75" s="85">
+        <v>0</v>
+      </c>
+      <c r="L75" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M75" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N75" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O75" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P75" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q75" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R75" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S75" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T75" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U75" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V75" s="85"/>
       <c r="W75" s="85"/>
       <c r="X75" s="85"/>
@@ -4238,27 +6836,69 @@
       <c r="AF75" s="85"/>
     </row>
     <row r="76">
-      <c r="A76" s="85"/>
-      <c r="B76" s="85"/>
-      <c r="C76" s="85"/>
-      <c r="D76" s="85"/>
-      <c r="E76" s="85"/>
-      <c r="F76" s="85"/>
-      <c r="G76" s="85"/>
-      <c r="H76" s="85"/>
-      <c r="I76" s="85"/>
-      <c r="J76" s="85"/>
-      <c r="K76" s="85"/>
-      <c r="L76" s="85"/>
-      <c r="M76" s="85"/>
-      <c r="N76" s="85"/>
-      <c r="O76" s="98"/>
-      <c r="P76" s="85"/>
-      <c r="Q76" s="85"/>
-      <c r="R76" s="85"/>
-      <c r="S76" s="85"/>
-      <c r="T76" s="85"/>
-      <c r="U76" s="85"/>
+      <c r="A76" s="85">
+        <v>65</v>
+      </c>
+      <c r="B76" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="F76" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="G76" s="85">
+        <v>10</v>
+      </c>
+      <c r="H76" s="85">
+        <v>14</v>
+      </c>
+      <c r="I76" s="85">
+        <v>140</v>
+      </c>
+      <c r="J76" s="85">
+        <v>0</v>
+      </c>
+      <c r="K76" s="85">
+        <v>0</v>
+      </c>
+      <c r="L76" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M76" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N76" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="O76" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="P76" s="85">
+        <v>11</v>
+      </c>
+      <c r="Q76" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="R76" s="85" t="s">
+        <v>4</v>
+      </c>
+      <c r="S76" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="T76" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U76" s="85" t="s">
+        <v>77</v>
+      </c>
       <c r="V76" s="85"/>
       <c r="W76" s="85"/>
       <c r="X76" s="85"/>

--- a/FreeLayout/Textfile/Export_Scraplist.xlsx
+++ b/FreeLayout/Textfile/Export_Scraplist.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t>MONTHLY SCRAP LIST</t>
   </si>
@@ -59,13 +59,13 @@
     <t>Month :</t>
   </si>
   <si>
-    <t>01</t>
+    <t>02</t>
   </si>
   <si>
     <t xml:space="preserve">Section : </t>
   </si>
   <si>
-    <t>PUR</t>
+    <t>PUS</t>
   </si>
   <si>
     <t>No.</t>
@@ -273,28 +273,40 @@
     <t>(34)</t>
   </si>
   <si>
-    <t>VE01</t>
+    <t>VR01</t>
+  </si>
+  <si>
+    <t>1198</t>
+  </si>
+  <si>
+    <t>MA6100</t>
+  </si>
+  <si>
+    <t>PUS_Door Phone</t>
+  </si>
+  <si>
+    <t>PNHG1053ZA/S1</t>
+  </si>
+  <si>
+    <t>Scrap PSNV cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANASONIC SYSTEM NETWORKS MALAYSIA SDN B </t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>A2KB0914E1/X1</t>
+    <t>IAF19788</t>
   </si>
   <si>
-    <t>Claim Scrap Material VB013 PUSVE26-3056</t>
+    <t>Missing part</t>
   </si>
   <si>
-    <t>PANASONIC GLOBAL PROCUREMENT</t>
+    <t>1.Other Issue Materials</t>
   </si>
   <si>
-    <t>9S98</t>
-  </si>
-  <si>
-    <t>IAF19566</t>
-  </si>
-  <si>
-    <t>PUSVE26-3056 : 1 pc</t>
+    <t>201</t>
   </si>
   <si>
     <t>ROH</t>
@@ -303,37 +315,262 @@
     <t>6210211000</t>
   </si>
   <si>
+    <t>VB012</t>
+  </si>
+  <si>
+    <t>V501</t>
+  </si>
+  <si>
+    <t>8198</t>
+  </si>
+  <si>
+    <t>MAX100</t>
+  </si>
+  <si>
+    <t>PUS_Refrigerator VN</t>
+  </si>
+  <si>
+    <t>AWW2431CEBC0-0C0</t>
+  </si>
+  <si>
+    <t>Scarp PSNV cost</t>
+  </si>
+  <si>
+    <t>RONNIE ELECTRONICS (J) SDN BHD</t>
+  </si>
+  <si>
+    <t>VF123</t>
+  </si>
+  <si>
+    <t>G0B502J00007</t>
+  </si>
+  <si>
+    <t>VF163</t>
+  </si>
+  <si>
+    <t>AWW2406C9UC0-0C2</t>
+  </si>
+  <si>
+    <t>PANASONIC GLOBAL PROCUREMENT (CHINA) CO., LTD</t>
+  </si>
+  <si>
     <t>VB013</t>
+  </si>
+  <si>
+    <t>VE01</t>
+  </si>
+  <si>
+    <t>9C98</t>
+  </si>
+  <si>
+    <t>MAC100</t>
+  </si>
+  <si>
+    <t>PUS_DSC CAMERA</t>
+  </si>
+  <si>
+    <t>DVME1522ZA/X1</t>
+  </si>
+  <si>
+    <t>PANASONIC HONG KONG CO., LIMITED - PANASONIC GLOBAL PROCUREMENT (HONG KONG) PHK-PGPRHK</t>
+  </si>
+  <si>
+    <t>VB011</t>
+  </si>
+  <si>
+    <t>DVUR1335ZA/X1</t>
+  </si>
+  <si>
+    <t>9S98</t>
+  </si>
+  <si>
+    <t>MAS100</t>
+  </si>
+  <si>
+    <t>PUS_SOUND BIZ</t>
+  </si>
+  <si>
+    <t>A8EC1036B3/C1</t>
+  </si>
+  <si>
+    <t>SUN-WA TECHNOS (VIETNAM) COMPANY LIMITED</t>
+  </si>
+  <si>
+    <t>VE100</t>
+  </si>
+  <si>
+    <t>PGUS1064ZA/C1</t>
+  </si>
+  <si>
+    <t>PRJ SMALL AMOUNT &lt;200 USD SCRAP PSNV COST</t>
+  </si>
+  <si>
+    <t>VB014Y</t>
+  </si>
+  <si>
+    <t>PGKM1221XA/C1</t>
+  </si>
+  <si>
+    <t>Claim Scrap Material/VE100/PUSVE26-3093</t>
+  </si>
+  <si>
+    <t>3.Material Shortage</t>
+  </si>
+  <si>
+    <t>6210300000</t>
   </si>
   <si>
     <t>PGMD1258ZA/C1</t>
   </si>
   <si>
-    <t>Scrap PSNV cost</t>
+    <t>PGJK1024ZA/V1</t>
   </si>
   <si>
-    <t>SUN-WA TECHNOS (VIETNAM) COMPANY</t>
+    <t xml:space="preserve">KINGLEY TECHNOLOGY INDUSTRIAL (VIETNAM) CO  LTD</t>
   </si>
   <si>
-    <t>VE100</t>
+    <t>VE017</t>
   </si>
   <si>
     <t>F4D55474A061</t>
   </si>
   <si>
-    <t>PRJ SMALL AMOUNT &lt;200 USD SCRAP PSNV COST</t>
-  </si>
-  <si>
-    <t>PANASONIC OPERATIONAL EXCELLENCE</t>
+    <t>PANASONIC OPERATIONAL EXCELLENCE CO LTD</t>
   </si>
   <si>
     <t>VB014</t>
   </si>
   <si>
+    <t>PGMH2378ZA/C1</t>
+  </si>
+  <si>
     <t>PGMD1257ZA/C1</t>
   </si>
   <si>
-    <t>PGMH2378ZA/C1</t>
+    <t>PGPW1051ZA/C1</t>
+  </si>
+  <si>
+    <t>PGJB1004ZA/C1</t>
+  </si>
+  <si>
+    <t>11D8</t>
+  </si>
+  <si>
+    <t>MA2100</t>
+  </si>
+  <si>
+    <t>PUS_TEL</t>
+  </si>
+  <si>
+    <t>PNJC1018ZB/Z1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.M.NAGANO (HK) LTD </t>
+  </si>
+  <si>
+    <t>VJ001</t>
+  </si>
+  <si>
+    <t>PNPK3895030PA/V3</t>
+  </si>
+  <si>
+    <t>VE115</t>
+  </si>
+  <si>
+    <t>PNKF1277ZB1K108/M1</t>
+  </si>
+  <si>
+    <t>PQHS10467YB/V2</t>
+  </si>
+  <si>
+    <t>FIT VIETNAM CO LTD</t>
+  </si>
+  <si>
+    <t>VE054</t>
+  </si>
+  <si>
+    <t>PNVE1011ZG/Z1</t>
+  </si>
+  <si>
+    <t>PNJT1142ZA/Z1</t>
+  </si>
+  <si>
+    <t>PNBC1591YA1K108/M1</t>
+  </si>
+  <si>
+    <t>PNJT1143ZA/Z1</t>
+  </si>
+  <si>
+    <t>PNMH1308ZA/M1</t>
+  </si>
+  <si>
+    <t>PNBC1354ZA1K108/V1</t>
+  </si>
+  <si>
+    <t>VIETDRAGON PRECISION PLASTIC LIMITED COMPANY</t>
+  </si>
+  <si>
+    <t>VE079</t>
+  </si>
+  <si>
+    <t>VMD5758</t>
+  </si>
+  <si>
+    <t>XQN16+BJ4FN</t>
+  </si>
+  <si>
+    <t>L0AA02A00161</t>
+  </si>
+  <si>
+    <t>ANHUI PROVINCE MINGTAI INC</t>
+  </si>
+  <si>
+    <t>VF158</t>
+  </si>
+  <si>
+    <t>PNLB2849ZA-AP</t>
+  </si>
+  <si>
+    <t>TSB VIETNAM CO LTD</t>
+  </si>
+  <si>
+    <t>VE055</t>
+  </si>
+  <si>
+    <t>PNLB2804ZA-YY</t>
+  </si>
+  <si>
+    <t>AOSHIKANG TECHNOLOGY (HONGKONG) CO LIMITTED</t>
+  </si>
+  <si>
+    <t>VF157</t>
+  </si>
+  <si>
+    <t>G4DYA0001054</t>
+  </si>
+  <si>
+    <t>VG01</t>
+  </si>
+  <si>
+    <t>6198</t>
+  </si>
+  <si>
+    <t>MAM100</t>
+  </si>
+  <si>
+    <t>PUS_MICROWAVE</t>
+  </si>
+  <si>
+    <t>F9035P90AP</t>
+  </si>
+  <si>
+    <t>H0920000BA</t>
+  </si>
+  <si>
+    <t>UNITED PRECISION ENGINEERING CO., LTD</t>
+  </si>
+  <si>
+    <t>VE076</t>
   </si>
 </sst>
 </file>
@@ -1731,63 +1968,57 @@
         <v>74</v>
       </c>
       <c r="D12" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="67" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="77">
+        <v>285</v>
+      </c>
+      <c r="H12" s="78">
+        <v>0.0146</v>
+      </c>
+      <c r="I12" s="90">
+        <v>0</v>
+      </c>
+      <c r="J12" s="78"/>
+      <c r="K12" s="90"/>
+      <c r="L12" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="N12" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="77">
-        <v>1</v>
-      </c>
-      <c r="H12" s="78">
-        <v>9.2827</v>
-      </c>
-      <c r="I12" s="90">
-        <f>TRUNC(G12*H12,5)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="78">
-        <v>9.3572</v>
-      </c>
-      <c r="K12" s="90">
-        <f>TRUNC(J12*G12,5)</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="79" t="s">
-        <v>76</v>
-      </c>
-      <c r="M12" s="79" t="s">
-        <v>77</v>
-      </c>
-      <c r="N12" s="80" t="s">
-        <v>78</v>
-      </c>
       <c r="O12" s="81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P12" s="65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q12" s="65" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R12" s="82" t="s">
         <v>4</v>
       </c>
       <c r="S12" s="83" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T12" s="83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U12" s="84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V12" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W12" s="74"/>
       <c r="X12" s="85"/>
@@ -1801,7 +2032,7 @@
       <c r="AF12" s="74"/>
       <c r="AG12" s="74"/>
       <c r="AH12" s="74" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="36" customFormat="1">
@@ -1809,67 +2040,63 @@
         <v>2</v>
       </c>
       <c r="B13" s="76" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D13" s="50" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E13" s="50" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="F13" s="67" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G13" s="77">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H13" s="78">
-        <v>0.5761</v>
+        <v>0.5114</v>
       </c>
       <c r="I13" s="90">
-        <f ref="I13:I76" t="shared" si="0">TRUNC(G13*H13,5)</f>
         <v>0</v>
       </c>
       <c r="J13" s="78"/>
-      <c r="K13" s="90">
-        <f ref="K13:K76" t="shared" si="1">TRUNC(J13*G13,5)</f>
-        <v>0</v>
-      </c>
+      <c r="K13" s="90"/>
       <c r="L13" s="79" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="M13" s="79" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="N13" s="80" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="O13" s="81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P13" s="65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q13" s="65" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R13" s="82" t="s">
         <v>4</v>
       </c>
       <c r="S13" s="83" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T13" s="83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U13" s="84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V13" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W13" s="74"/>
       <c r="X13" s="85"/>
@@ -1883,7 +2110,7 @@
       <c r="AF13" s="74"/>
       <c r="AG13" s="74"/>
       <c r="AH13" s="74" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="36" customFormat="1">
@@ -1891,67 +2118,63 @@
         <v>3</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C14" s="54" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D14" s="50" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E14" s="50" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="F14" s="67" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G14" s="77">
         <v>1</v>
       </c>
       <c r="H14" s="78">
-        <v>3.34702</v>
+        <v>0.91</v>
       </c>
       <c r="I14" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J14" s="78"/>
-      <c r="K14" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="K14" s="90"/>
       <c r="L14" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="N14" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="M14" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="N14" s="80" t="s">
-        <v>78</v>
-      </c>
       <c r="O14" s="81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P14" s="65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q14" s="65" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="R14" s="82" t="s">
         <v>4</v>
       </c>
       <c r="S14" s="83" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T14" s="83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U14" s="84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V14" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W14" s="74"/>
       <c r="X14" s="85"/>
@@ -1965,7 +2188,7 @@
       <c r="AF14" s="74"/>
       <c r="AG14" s="74"/>
       <c r="AH14" s="74" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="36" customFormat="1">
@@ -1973,67 +2196,63 @@
         <v>4</v>
       </c>
       <c r="B15" s="76" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="C15" s="54" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D15" s="50" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="F15" s="67" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G15" s="77">
         <v>1</v>
       </c>
       <c r="H15" s="78">
-        <v>1.7755</v>
+        <v>0.7438</v>
       </c>
       <c r="I15" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J15" s="78"/>
-      <c r="K15" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="K15" s="90"/>
       <c r="L15" s="79" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M15" s="79" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="N15" s="80" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="O15" s="81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P15" s="65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="65" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R15" s="82" t="s">
         <v>4</v>
       </c>
       <c r="S15" s="83" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T15" s="83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U15" s="84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V15" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W15" s="74"/>
       <c r="X15" s="85"/>
@@ -2047,7 +2266,7 @@
       <c r="AF15" s="74"/>
       <c r="AG15" s="74"/>
       <c r="AH15" s="74" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="36" customFormat="1">
@@ -2055,67 +2274,63 @@
         <v>5</v>
       </c>
       <c r="B16" s="76" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="C16" s="54" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D16" s="50" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E16" s="50" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="F16" s="67" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G16" s="77">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="H16" s="78">
-        <v>0.092</v>
+        <v>0.07093</v>
       </c>
       <c r="I16" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J16" s="78"/>
-      <c r="K16" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="K16" s="90"/>
       <c r="L16" s="79" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M16" s="79" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="N16" s="80" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="O16" s="81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="P16" s="65" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q16" s="65" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="R16" s="82" t="s">
         <v>4</v>
       </c>
       <c r="S16" s="83" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="T16" s="83" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="U16" s="84" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V16" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="W16" s="74"/>
       <c r="X16" s="85"/>
@@ -2129,38 +2344,72 @@
       <c r="AF16" s="74"/>
       <c r="AG16" s="74"/>
       <c r="AH16" s="74" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="36" customFormat="1">
-      <c r="A17" s="75"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="78"/>
+      <c r="A17" s="75">
+        <v>6</v>
+      </c>
+      <c r="B17" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="67" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17" s="77">
+        <v>120</v>
+      </c>
+      <c r="H17" s="78">
+        <v>0.01363</v>
+      </c>
       <c r="I17" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J17" s="78"/>
-      <c r="K17" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="79"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="65"/>
-      <c r="Q17" s="65"/>
-      <c r="R17" s="82"/>
-      <c r="S17" s="83"/>
-      <c r="T17" s="83"/>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
+      <c r="K17" s="90"/>
+      <c r="L17" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="M17" s="79" t="s">
+        <v>106</v>
+      </c>
+      <c r="N17" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="P17" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q17" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="R17" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="T17" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="U17" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="V17" s="84" t="s">
+        <v>86</v>
+      </c>
       <c r="W17" s="74"/>
       <c r="X17" s="85"/>
       <c r="Y17" s="74"/>
@@ -2172,37 +2421,73 @@
       <c r="AE17" s="74"/>
       <c r="AF17" s="74"/>
       <c r="AG17" s="74"/>
-      <c r="AH17" s="74"/>
+      <c r="AH17" s="74" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="36" customFormat="1">
-      <c r="A18" s="75"/>
-      <c r="B18" s="76"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="78"/>
+      <c r="A18" s="75">
+        <v>7</v>
+      </c>
+      <c r="B18" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="67" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="77">
+        <v>20</v>
+      </c>
+      <c r="H18" s="78">
+        <v>1.3017</v>
+      </c>
       <c r="I18" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J18" s="78"/>
-      <c r="K18" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="81"/>
-      <c r="P18" s="65"/>
-      <c r="Q18" s="65"/>
-      <c r="R18" s="82"/>
-      <c r="S18" s="83"/>
-      <c r="T18" s="83"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="84"/>
+      <c r="K18" s="90"/>
+      <c r="L18" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="M18" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="N18" s="80" t="s">
+        <v>109</v>
+      </c>
+      <c r="O18" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="P18" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q18" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="R18" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="T18" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="U18" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="V18" s="84" t="s">
+        <v>86</v>
+      </c>
       <c r="W18" s="74"/>
       <c r="X18" s="85"/>
       <c r="Y18" s="74"/>
@@ -2214,37 +2499,73 @@
       <c r="AE18" s="74"/>
       <c r="AF18" s="74"/>
       <c r="AG18" s="74"/>
-      <c r="AH18" s="74"/>
+      <c r="AH18" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" s="36" customFormat="1">
-      <c r="A19" s="75"/>
-      <c r="B19" s="76"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="67"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="78"/>
+      <c r="A19" s="75">
+        <v>8</v>
+      </c>
+      <c r="B19" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="67" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="77">
+        <v>10</v>
+      </c>
+      <c r="H19" s="78">
+        <v>1.30867</v>
+      </c>
       <c r="I19" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J19" s="78"/>
-      <c r="K19" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="81"/>
-      <c r="P19" s="65"/>
-      <c r="Q19" s="65"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="83"/>
-      <c r="T19" s="83"/>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="N19" s="80" t="s">
+        <v>109</v>
+      </c>
+      <c r="O19" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="P19" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q19" s="65" t="s">
+        <v>82</v>
+      </c>
+      <c r="R19" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="S19" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="T19" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="U19" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="V19" s="84" t="s">
+        <v>86</v>
+      </c>
       <c r="W19" s="74"/>
       <c r="X19" s="85"/>
       <c r="Y19" s="74"/>
@@ -2256,37 +2577,77 @@
       <c r="AE19" s="74"/>
       <c r="AF19" s="74"/>
       <c r="AG19" s="74"/>
-      <c r="AH19" s="74"/>
+      <c r="AH19" s="74" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" s="36" customFormat="1">
-      <c r="A20" s="69"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="78"/>
+      <c r="A20" s="69">
+        <v>9</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="59">
+        <v>25</v>
+      </c>
+      <c r="H20" s="78">
+        <v>0.4136</v>
+      </c>
       <c r="I20" s="90">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="78"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="78">
+        <v>0.4136</v>
+      </c>
       <c r="K20" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="54"/>
-      <c r="M20" s="54"/>
-      <c r="N20" s="54"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="65"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="67"/>
-      <c r="S20" s="57"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="M20" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="N20" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="P20" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q20" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="R20" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="T20" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="U20" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="V20" s="58" t="s">
+        <v>121</v>
+      </c>
       <c r="W20" s="38"/>
       <c r="X20" s="39"/>
       <c r="Y20" s="38"/>
@@ -2298,37 +2659,73 @@
       <c r="AE20" s="38"/>
       <c r="AF20" s="38"/>
       <c r="AG20" s="38"/>
-      <c r="AH20" s="74"/>
+      <c r="AH20" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="70"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="78"/>
+      <c r="A21" s="70">
+        <v>10</v>
+      </c>
+      <c r="B21" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="60">
+        <v>10</v>
+      </c>
+      <c r="H21" s="78">
+        <v>0.5761</v>
+      </c>
       <c r="I21" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="78"/>
-      <c r="K21" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="56"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="48"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="48"/>
-      <c r="V21" s="48"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="56" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="N21" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="O21" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="P21" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q21" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R21" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T21" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U21" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V21" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W21" s="41"/>
       <c r="X21" s="41"/>
       <c r="Y21" s="41"/>
@@ -2340,37 +2737,73 @@
       <c r="AE21" s="41"/>
       <c r="AF21" s="41"/>
       <c r="AG21" s="41"/>
-      <c r="AH21" s="74"/>
+      <c r="AH21" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="22" s="25" customFormat="1">
-      <c r="A22" s="71"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="78"/>
+      <c r="A22" s="71">
+        <v>11</v>
+      </c>
+      <c r="B22" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F22" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="G22" s="61">
+        <v>180</v>
+      </c>
+      <c r="H22" s="78">
+        <v>0.0271</v>
+      </c>
       <c r="I22" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J22" s="78"/>
-      <c r="K22" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="44"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="53"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="53"/>
+      <c r="K22" s="90"/>
+      <c r="L22" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="N22" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O22" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P22" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q22" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R22" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T22" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U22" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V22" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W22" s="43"/>
       <c r="X22" s="43"/>
       <c r="Y22" s="43"/>
@@ -2382,37 +2815,73 @@
       <c r="AE22" s="43"/>
       <c r="AF22" s="43"/>
       <c r="AG22" s="43"/>
-      <c r="AH22" s="74"/>
+      <c r="AH22" s="74" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="23" s="25" customFormat="1">
-      <c r="A23" s="71"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="47"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="78"/>
+      <c r="A23" s="71">
+        <v>12</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C23" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="G23" s="61">
+        <v>1</v>
+      </c>
+      <c r="H23" s="78">
+        <v>3.34702</v>
+      </c>
       <c r="I23" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J23" s="78"/>
-      <c r="K23" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="44"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="M23" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="N23" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O23" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P23" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q23" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R23" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T23" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U23" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V23" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W23" s="43"/>
       <c r="X23" s="43"/>
       <c r="Y23" s="43"/>
@@ -2424,37 +2893,73 @@
       <c r="AE23" s="43"/>
       <c r="AF23" s="43"/>
       <c r="AG23" s="43"/>
-      <c r="AH23" s="74"/>
+      <c r="AH23" s="74" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="24" s="25" customFormat="1">
-      <c r="A24" s="71"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="78"/>
+      <c r="A24" s="71">
+        <v>13</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="47" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="61">
+        <v>28</v>
+      </c>
+      <c r="H24" s="78">
+        <v>0.092</v>
+      </c>
       <c r="I24" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J24" s="78"/>
-      <c r="K24" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="47"/>
-      <c r="Q24" s="47"/>
-      <c r="R24" s="47"/>
-      <c r="S24" s="53"/>
-      <c r="T24" s="53"/>
-      <c r="U24" s="53"/>
-      <c r="V24" s="53"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="N24" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P24" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q24" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R24" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T24" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U24" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V24" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W24" s="43"/>
       <c r="X24" s="43"/>
       <c r="Y24" s="43"/>
@@ -2466,37 +2971,73 @@
       <c r="AE24" s="43"/>
       <c r="AF24" s="43"/>
       <c r="AG24" s="43"/>
-      <c r="AH24" s="74"/>
+      <c r="AH24" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="25" s="25" customFormat="1">
-      <c r="A25" s="71"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="78"/>
+      <c r="A25" s="71">
+        <v>14</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="61">
+        <v>1</v>
+      </c>
+      <c r="H25" s="78">
+        <v>1.7755</v>
+      </c>
       <c r="I25" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J25" s="78"/>
-      <c r="K25" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="47"/>
-      <c r="Q25" s="47"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="53"/>
-      <c r="T25" s="53"/>
-      <c r="U25" s="53"/>
-      <c r="V25" s="53"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M25" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="N25" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P25" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q25" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R25" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S25" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T25" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U25" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V25" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W25" s="43"/>
       <c r="X25" s="43"/>
       <c r="Y25" s="43"/>
@@ -2508,37 +3049,73 @@
       <c r="AE25" s="43"/>
       <c r="AF25" s="43"/>
       <c r="AG25" s="43"/>
-      <c r="AH25" s="74"/>
+      <c r="AH25" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="26" s="25" customFormat="1">
-      <c r="A26" s="71"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="47"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="78"/>
+      <c r="A26" s="71">
+        <v>15</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="61">
+        <v>1</v>
+      </c>
+      <c r="H26" s="78">
+        <v>1.14403</v>
+      </c>
       <c r="I26" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J26" s="78"/>
-      <c r="K26" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="47"/>
-      <c r="Q26" s="47"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="53"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="53"/>
-      <c r="V26" s="53"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="M26" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P26" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q26" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R26" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T26" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U26" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V26" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W26" s="43"/>
       <c r="X26" s="43"/>
       <c r="Y26" s="43"/>
@@ -2550,37 +3127,73 @@
       <c r="AE26" s="43"/>
       <c r="AF26" s="43"/>
       <c r="AG26" s="43"/>
-      <c r="AH26" s="74"/>
+      <c r="AH26" s="74" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="27" s="25" customFormat="1">
-      <c r="A27" s="71"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="78"/>
+      <c r="A27" s="71">
+        <v>16</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="61">
+        <v>3</v>
+      </c>
+      <c r="H27" s="78">
+        <v>0.2464</v>
+      </c>
       <c r="I27" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J27" s="78"/>
-      <c r="K27" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="53"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="53"/>
-      <c r="V27" s="53"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M27" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="N27" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P27" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q27" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R27" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T27" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U27" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V27" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W27" s="43"/>
       <c r="X27" s="43"/>
       <c r="Y27" s="43"/>
@@ -2592,37 +3205,73 @@
       <c r="AE27" s="43"/>
       <c r="AF27" s="43"/>
       <c r="AG27" s="43"/>
-      <c r="AH27" s="74"/>
+      <c r="AH27" s="74" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="28" s="25" customFormat="1">
-      <c r="A28" s="71"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="47"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="78"/>
+      <c r="A28" s="71">
+        <v>17</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F28" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="61">
+        <v>180</v>
+      </c>
+      <c r="H28" s="78">
+        <v>0.021</v>
+      </c>
       <c r="I28" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J28" s="78"/>
-      <c r="K28" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="47"/>
-      <c r="Q28" s="47"/>
-      <c r="R28" s="47"/>
-      <c r="S28" s="53"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="53"/>
-      <c r="V28" s="53"/>
+      <c r="K28" s="90"/>
+      <c r="L28" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M28" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="N28" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P28" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q28" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R28" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S28" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T28" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U28" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V28" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W28" s="43"/>
       <c r="X28" s="43"/>
       <c r="Y28" s="43"/>
@@ -2634,37 +3283,73 @@
       <c r="AE28" s="43"/>
       <c r="AF28" s="43"/>
       <c r="AG28" s="43"/>
-      <c r="AH28" s="74"/>
+      <c r="AH28" s="74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="29" s="25" customFormat="1">
-      <c r="A29" s="71"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="78"/>
+      <c r="A29" s="71">
+        <v>18</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F29" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="G29" s="61">
+        <v>10</v>
+      </c>
+      <c r="H29" s="78">
+        <v>0.34763</v>
+      </c>
       <c r="I29" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J29" s="78"/>
-      <c r="K29" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="53"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="53"/>
-      <c r="V29" s="53"/>
+      <c r="K29" s="90"/>
+      <c r="L29" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M29" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="N29" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O29" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P29" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q29" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R29" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T29" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U29" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V29" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W29" s="43"/>
       <c r="X29" s="43"/>
       <c r="Y29" s="43"/>
@@ -2676,37 +3361,73 @@
       <c r="AE29" s="43"/>
       <c r="AF29" s="43"/>
       <c r="AG29" s="43"/>
-      <c r="AH29" s="74"/>
+      <c r="AH29" s="74" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="30" s="25" customFormat="1">
-      <c r="A30" s="71"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="78"/>
+      <c r="A30" s="71">
+        <v>19</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="61">
+        <v>12</v>
+      </c>
+      <c r="H30" s="78">
+        <v>0.1825</v>
+      </c>
       <c r="I30" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J30" s="78"/>
-      <c r="K30" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="53"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="53"/>
-      <c r="V30" s="53"/>
+      <c r="K30" s="90"/>
+      <c r="L30" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M30" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="N30" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O30" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P30" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q30" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R30" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S30" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T30" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U30" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V30" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W30" s="43"/>
       <c r="X30" s="43"/>
       <c r="Y30" s="43"/>
@@ -2718,37 +3439,73 @@
       <c r="AE30" s="43"/>
       <c r="AF30" s="43"/>
       <c r="AG30" s="43"/>
-      <c r="AH30" s="74"/>
+      <c r="AH30" s="74" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="31" s="25" customFormat="1">
-      <c r="A31" s="71"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="78"/>
+      <c r="A31" s="71">
+        <v>20</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D31" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="G31" s="61">
+        <v>180</v>
+      </c>
+      <c r="H31" s="78">
+        <v>0.0121</v>
+      </c>
       <c r="I31" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J31" s="78"/>
-      <c r="K31" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47"/>
-      <c r="S31" s="53"/>
-      <c r="T31" s="53"/>
-      <c r="U31" s="53"/>
-      <c r="V31" s="53"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M31" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="N31" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O31" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P31" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q31" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R31" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S31" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T31" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U31" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V31" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W31" s="43"/>
       <c r="X31" s="43"/>
       <c r="Y31" s="43"/>
@@ -2760,37 +3517,73 @@
       <c r="AE31" s="43"/>
       <c r="AF31" s="43"/>
       <c r="AG31" s="43"/>
-      <c r="AH31" s="74"/>
+      <c r="AH31" s="74" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="32" s="25" customFormat="1">
-      <c r="A32" s="71"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="78"/>
+      <c r="A32" s="71">
+        <v>21</v>
+      </c>
+      <c r="B32" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D32" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="61">
+        <v>33</v>
+      </c>
+      <c r="H32" s="78">
+        <v>0.0539</v>
+      </c>
       <c r="I32" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J32" s="78"/>
-      <c r="K32" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="47"/>
-      <c r="N32" s="47"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="47"/>
-      <c r="Q32" s="47"/>
-      <c r="R32" s="47"/>
-      <c r="S32" s="53"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
-      <c r="V32" s="53"/>
+      <c r="K32" s="90"/>
+      <c r="L32" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M32" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="N32" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O32" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P32" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q32" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R32" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T32" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U32" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V32" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W32" s="43"/>
       <c r="X32" s="43"/>
       <c r="Y32" s="43"/>
@@ -2802,37 +3595,73 @@
       <c r="AE32" s="43"/>
       <c r="AF32" s="43"/>
       <c r="AG32" s="43"/>
-      <c r="AH32" s="74"/>
+      <c r="AH32" s="74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="33" s="25" customFormat="1">
-      <c r="A33" s="71"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="78"/>
+      <c r="A33" s="71">
+        <v>22</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="47" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33" s="61">
+        <v>110</v>
+      </c>
+      <c r="H33" s="78">
+        <v>0.0131</v>
+      </c>
       <c r="I33" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J33" s="78"/>
-      <c r="K33" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47"/>
-      <c r="R33" s="47"/>
-      <c r="S33" s="53"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="53"/>
-      <c r="V33" s="53"/>
+      <c r="K33" s="90"/>
+      <c r="L33" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M33" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="N33" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P33" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q33" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R33" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T33" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U33" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V33" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W33" s="43"/>
       <c r="X33" s="43"/>
       <c r="Y33" s="43"/>
@@ -2844,37 +3673,73 @@
       <c r="AE33" s="43"/>
       <c r="AF33" s="43"/>
       <c r="AG33" s="43"/>
-      <c r="AH33" s="74"/>
+      <c r="AH33" s="74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="34" s="25" customFormat="1">
-      <c r="A34" s="71"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="78"/>
+      <c r="A34" s="71">
+        <v>23</v>
+      </c>
+      <c r="B34" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F34" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="G34" s="61">
+        <v>30</v>
+      </c>
+      <c r="H34" s="78">
+        <v>0.0436</v>
+      </c>
       <c r="I34" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J34" s="78"/>
-      <c r="K34" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
-      <c r="N34" s="47"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="47"/>
-      <c r="Q34" s="47"/>
-      <c r="R34" s="47"/>
-      <c r="S34" s="53"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="53"/>
-      <c r="V34" s="53"/>
+      <c r="K34" s="90"/>
+      <c r="L34" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M34" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="N34" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O34" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P34" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q34" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R34" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S34" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T34" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U34" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V34" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W34" s="43"/>
       <c r="X34" s="43"/>
       <c r="Y34" s="43"/>
@@ -2886,37 +3751,73 @@
       <c r="AE34" s="43"/>
       <c r="AF34" s="43"/>
       <c r="AG34" s="43"/>
-      <c r="AH34" s="74"/>
+      <c r="AH34" s="74" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" s="25" customFormat="1">
-      <c r="A35" s="71"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="47"/>
-      <c r="D35" s="47"/>
-      <c r="E35" s="47"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="78"/>
+      <c r="A35" s="71">
+        <v>24</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="G35" s="61">
+        <v>90</v>
+      </c>
+      <c r="H35" s="78">
+        <v>0.0141</v>
+      </c>
       <c r="I35" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J35" s="78"/>
-      <c r="K35" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="44"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="53"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="53"/>
-      <c r="V35" s="53"/>
+      <c r="K35" s="90"/>
+      <c r="L35" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M35" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="N35" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O35" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P35" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q35" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R35" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T35" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U35" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V35" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W35" s="43"/>
       <c r="X35" s="43"/>
       <c r="Y35" s="43"/>
@@ -2928,37 +3829,73 @@
       <c r="AE35" s="43"/>
       <c r="AF35" s="43"/>
       <c r="AG35" s="43"/>
-      <c r="AH35" s="74"/>
+      <c r="AH35" s="74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="36" s="25" customFormat="1">
-      <c r="A36" s="71"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="47"/>
-      <c r="D36" s="47"/>
-      <c r="E36" s="47"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="78"/>
+      <c r="A36" s="71">
+        <v>25</v>
+      </c>
+      <c r="B36" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F36" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="61">
+        <v>20</v>
+      </c>
+      <c r="H36" s="78">
+        <v>0.0111</v>
+      </c>
       <c r="I36" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J36" s="78"/>
-      <c r="K36" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L36" s="47"/>
-      <c r="M36" s="47"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="44"/>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47"/>
-      <c r="S36" s="53"/>
-      <c r="T36" s="53"/>
-      <c r="U36" s="53"/>
-      <c r="V36" s="53"/>
+      <c r="K36" s="90"/>
+      <c r="L36" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M36" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="N36" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O36" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P36" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q36" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R36" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S36" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T36" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U36" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V36" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W36" s="43"/>
       <c r="X36" s="43"/>
       <c r="Y36" s="43"/>
@@ -2970,37 +3907,73 @@
       <c r="AE36" s="43"/>
       <c r="AF36" s="43"/>
       <c r="AG36" s="43"/>
-      <c r="AH36" s="74"/>
+      <c r="AH36" s="74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="37" s="25" customFormat="1">
-      <c r="A37" s="72"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="78"/>
+      <c r="A37" s="72">
+        <v>26</v>
+      </c>
+      <c r="B37" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="D37" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" s="47" t="s">
+        <v>135</v>
+      </c>
+      <c r="F37" s="47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G37" s="61">
+        <v>2</v>
+      </c>
+      <c r="H37" s="78">
+        <v>0.0189</v>
+      </c>
       <c r="I37" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J37" s="78"/>
-      <c r="K37" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="47"/>
-      <c r="M37" s="47"/>
-      <c r="N37" s="47"/>
-      <c r="O37" s="44"/>
-      <c r="P37" s="47"/>
-      <c r="Q37" s="47"/>
-      <c r="R37" s="47"/>
-      <c r="S37" s="53"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="53"/>
-      <c r="V37" s="53"/>
+      <c r="K37" s="90"/>
+      <c r="L37" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M37" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="N37" s="47" t="s">
+        <v>133</v>
+      </c>
+      <c r="O37" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P37" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q37" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S37" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T37" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U37" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V37" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W37" s="43"/>
       <c r="X37" s="43"/>
       <c r="Y37" s="43"/>
@@ -3012,37 +3985,73 @@
       <c r="AE37" s="43"/>
       <c r="AF37" s="43"/>
       <c r="AG37" s="43"/>
-      <c r="AH37" s="74"/>
+      <c r="AH37" s="74" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="38" s="25" customFormat="1">
-      <c r="A38" s="71"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="78"/>
+      <c r="A38" s="71">
+        <v>27</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C38" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E38" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="G38" s="61">
+        <v>134</v>
+      </c>
+      <c r="H38" s="78">
+        <v>0.00529</v>
+      </c>
       <c r="I38" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J38" s="78"/>
-      <c r="K38" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
-      <c r="N38" s="47"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="47"/>
-      <c r="Q38" s="47"/>
-      <c r="R38" s="47"/>
-      <c r="S38" s="53"/>
-      <c r="T38" s="53"/>
-      <c r="U38" s="53"/>
-      <c r="V38" s="53"/>
+      <c r="K38" s="90"/>
+      <c r="L38" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="M38" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="N38" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="O38" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="P38" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q38" s="47" t="s">
+        <v>82</v>
+      </c>
+      <c r="R38" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="S38" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="T38" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="U38" s="53" t="s">
+        <v>85</v>
+      </c>
+      <c r="V38" s="53" t="s">
+        <v>86</v>
+      </c>
       <c r="W38" s="43"/>
       <c r="X38" s="43"/>
       <c r="Y38" s="43"/>
@@ -3054,37 +4063,73 @@
       <c r="AE38" s="43"/>
       <c r="AF38" s="43"/>
       <c r="AG38" s="43"/>
-      <c r="AH38" s="74"/>
+      <c r="AH38" s="74" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="70"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="62"/>
-      <c r="H39" s="78"/>
+      <c r="A39" s="70">
+        <v>28</v>
+      </c>
+      <c r="B39" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G39" s="62">
+        <v>103</v>
+      </c>
+      <c r="H39" s="78">
+        <v>0.0025</v>
+      </c>
       <c r="I39" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J39" s="78"/>
-      <c r="K39" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L39" s="51"/>
-      <c r="M39" s="51"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="45"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="48"/>
-      <c r="T39" s="48"/>
-      <c r="U39" s="48"/>
-      <c r="V39" s="48"/>
+      <c r="K39" s="90"/>
+      <c r="L39" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M39" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="N39" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="O39" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P39" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q39" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R39" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S39" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T39" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U39" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V39" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W39" s="41"/>
       <c r="X39" s="41"/>
       <c r="Y39" s="41"/>
@@ -3096,37 +4141,73 @@
       <c r="AE39" s="41"/>
       <c r="AF39" s="41"/>
       <c r="AG39" s="41"/>
-      <c r="AH39" s="74"/>
+      <c r="AH39" s="74" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="70"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="51"/>
-      <c r="G40" s="62"/>
-      <c r="H40" s="78"/>
+      <c r="A40" s="70">
+        <v>29</v>
+      </c>
+      <c r="B40" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="G40" s="62">
+        <v>26</v>
+      </c>
+      <c r="H40" s="78">
+        <v>0.1289</v>
+      </c>
       <c r="I40" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J40" s="78"/>
-      <c r="K40" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="51"/>
-      <c r="M40" s="51"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="48"/>
-      <c r="T40" s="48"/>
-      <c r="U40" s="48"/>
-      <c r="V40" s="48"/>
+      <c r="K40" s="90"/>
+      <c r="L40" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M40" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="N40" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="O40" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P40" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q40" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R40" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S40" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T40" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U40" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V40" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W40" s="41"/>
       <c r="X40" s="41"/>
       <c r="Y40" s="41"/>
@@ -3138,37 +4219,73 @@
       <c r="AE40" s="41"/>
       <c r="AF40" s="41"/>
       <c r="AG40" s="41"/>
-      <c r="AH40" s="74"/>
+      <c r="AH40" s="74" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="70"/>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="78"/>
+      <c r="A41" s="70">
+        <v>30</v>
+      </c>
+      <c r="B41" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F41" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G41" s="62">
+        <v>6</v>
+      </c>
+      <c r="H41" s="78">
+        <v>0.3143</v>
+      </c>
       <c r="I41" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J41" s="78"/>
-      <c r="K41" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="45"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="48"/>
-      <c r="T41" s="48"/>
-      <c r="U41" s="48"/>
-      <c r="V41" s="48"/>
+      <c r="K41" s="90"/>
+      <c r="L41" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M41" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="N41" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="O41" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P41" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q41" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R41" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S41" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T41" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U41" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V41" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W41" s="41"/>
       <c r="X41" s="41"/>
       <c r="Y41" s="41"/>
@@ -3180,37 +4297,73 @@
       <c r="AE41" s="41"/>
       <c r="AF41" s="41"/>
       <c r="AG41" s="41"/>
-      <c r="AH41" s="74"/>
+      <c r="AH41" s="74" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="70"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="62"/>
-      <c r="H42" s="78"/>
+      <c r="A42" s="70">
+        <v>31</v>
+      </c>
+      <c r="B42" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F42" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" s="62">
+        <v>4</v>
+      </c>
+      <c r="H42" s="78">
+        <v>0.2068</v>
+      </c>
       <c r="I42" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J42" s="78"/>
-      <c r="K42" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L42" s="51"/>
-      <c r="M42" s="51"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="45"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="51"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="48"/>
-      <c r="T42" s="48"/>
-      <c r="U42" s="48"/>
-      <c r="V42" s="48"/>
+      <c r="K42" s="90"/>
+      <c r="L42" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M42" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="N42" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="O42" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P42" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q42" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R42" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S42" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T42" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U42" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V42" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W42" s="41"/>
       <c r="X42" s="41"/>
       <c r="Y42" s="41"/>
@@ -3222,37 +4375,73 @@
       <c r="AE42" s="41"/>
       <c r="AF42" s="41"/>
       <c r="AG42" s="41"/>
-      <c r="AH42" s="74"/>
+      <c r="AH42" s="74" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="70"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="62"/>
-      <c r="H43" s="78"/>
+      <c r="A43" s="70">
+        <v>32</v>
+      </c>
+      <c r="B43" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G43" s="62">
+        <v>1</v>
+      </c>
+      <c r="H43" s="78">
+        <v>0.299</v>
+      </c>
       <c r="I43" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J43" s="78"/>
-      <c r="K43" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L43" s="51"/>
-      <c r="M43" s="51"/>
-      <c r="N43" s="51"/>
-      <c r="O43" s="45"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="51"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="48"/>
-      <c r="T43" s="48"/>
-      <c r="U43" s="48"/>
-      <c r="V43" s="48"/>
+      <c r="K43" s="90"/>
+      <c r="L43" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M43" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="N43" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="O43" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P43" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q43" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R43" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S43" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T43" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U43" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V43" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W43" s="41"/>
       <c r="X43" s="41"/>
       <c r="Y43" s="41"/>
@@ -3264,37 +4453,73 @@
       <c r="AE43" s="41"/>
       <c r="AF43" s="41"/>
       <c r="AG43" s="41"/>
-      <c r="AH43" s="74"/>
+      <c r="AH43" s="74" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="70"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="51"/>
-      <c r="G44" s="62"/>
-      <c r="H44" s="78"/>
+      <c r="A44" s="70">
+        <v>33</v>
+      </c>
+      <c r="B44" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="F44" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G44" s="62">
+        <v>60</v>
+      </c>
+      <c r="H44" s="78">
+        <v>0.1607</v>
+      </c>
       <c r="I44" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J44" s="78"/>
-      <c r="K44" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L44" s="51"/>
-      <c r="M44" s="51"/>
-      <c r="N44" s="51"/>
-      <c r="O44" s="45"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="51"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="48"/>
-      <c r="T44" s="48"/>
-      <c r="U44" s="48"/>
-      <c r="V44" s="48"/>
+      <c r="K44" s="90"/>
+      <c r="L44" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M44" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="N44" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="O44" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P44" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q44" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R44" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S44" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T44" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U44" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V44" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W44" s="41"/>
       <c r="X44" s="41"/>
       <c r="Y44" s="41"/>
@@ -3306,37 +4531,73 @@
       <c r="AE44" s="41"/>
       <c r="AF44" s="41"/>
       <c r="AG44" s="41"/>
-      <c r="AH44" s="74"/>
+      <c r="AH44" s="74" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="70"/>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="62"/>
-      <c r="H45" s="78"/>
+      <c r="A45" s="70">
+        <v>34</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="D45" s="51" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="51" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="62">
+        <v>30</v>
+      </c>
+      <c r="H45" s="78">
+        <v>0.0014</v>
+      </c>
       <c r="I45" s="90">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J45" s="78"/>
-      <c r="K45" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L45" s="51"/>
-      <c r="M45" s="51"/>
-      <c r="N45" s="51"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="51"/>
-      <c r="S45" s="48"/>
-      <c r="T45" s="48"/>
-      <c r="U45" s="48"/>
-      <c r="V45" s="48"/>
+      <c r="K45" s="90"/>
+      <c r="L45" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="N45" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="O45" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="P45" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q45" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="R45" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="S45" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="T45" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="U45" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="V45" s="48" t="s">
+        <v>86</v>
+      </c>
       <c r="W45" s="41"/>
       <c r="X45" s="41"/>
       <c r="Y45" s="41"/>
@@ -3348,7 +4609,9 @@
       <c r="AE45" s="41"/>
       <c r="AF45" s="41"/>
       <c r="AG45" s="41"/>
-      <c r="AH45" s="74"/>
+      <c r="AH45" s="74" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="70"/>
@@ -3360,12 +4623,12 @@
       <c r="G46" s="62"/>
       <c r="H46" s="78"/>
       <c r="I46" s="90">
-        <f t="shared" si="0"/>
+        <f ref="I46:I76" t="shared" si="0">TRUNC(G46*H46,5)</f>
         <v>0</v>
       </c>
       <c r="J46" s="78"/>
       <c r="K46" s="90">
-        <f t="shared" si="1"/>
+        <f ref="K46:K76" t="shared" si="1">TRUNC(J46*G46,5)</f>
         <v>0</v>
       </c>
       <c r="L46" s="51"/>
